--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.023</v>
+        <v>0.227</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>0.021</v>
       </c>
       <c r="E7" t="n">
-        <v>0.013</v>
+        <v>0.206</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.074</v>
+        <v>-0.143</v>
       </c>
       <c r="D8" t="n">
         <v>-0.042</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.007</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.026</v>
+        <v>-0.002</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.019</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.392</v>
+        <v>-0.024</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
       <c r="E10" t="n">
-        <v>0.362</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.002</v>
+        <v>-0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.024</v>
+        <v>0.107</v>
       </c>
       <c r="D12" t="n">
-        <v>0.027</v>
+        <v>0.042</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.113</v>
+        <v>0.007</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.05</v>
+        <v>0.026</v>
       </c>
       <c r="E13" t="n">
-        <v>0.063</v>
+        <v>-0.019</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.034</v>
+        <v>-0.128</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.008</v>
+        <v>0.019</v>
       </c>
       <c r="E14" t="n">
-        <v>0.026</v>
+        <v>0.109</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.054</v>
+        <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.028</v>
+        <v>-0.013</v>
       </c>
       <c r="E15" t="n">
-        <v>0.026</v>
+        <v>-0.008</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0</v>
+        <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.004</v>
+        <v>0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.004</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.014</v>
+        <v>0.046</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E17" t="n">
-        <v>0.011</v>
+        <v>0.044</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.008</v>
+        <v>0.392</v>
       </c>
       <c r="D18" t="n">
-        <v>-0</v>
+        <v>0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>0.008</v>
+        <v>0.362</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.143</v>
+        <v>-0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.042</v>
+        <v>-0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.101</v>
+        <v>0.008</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.401</v>
+        <v>0.197</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.037</v>
+        <v>0.065</v>
       </c>
       <c r="E20" t="n">
-        <v>0.364</v>
+        <v>0.132</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.107</v>
+        <v>-0.074</v>
       </c>
       <c r="D21" t="n">
-        <v>0.042</v>
+        <v>-0.042</v>
       </c>
       <c r="E21" t="n">
-        <v>0.065</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.128</v>
+        <v>-0.113</v>
       </c>
       <c r="D22" t="n">
-        <v>0.019</v>
+        <v>-0.05</v>
       </c>
       <c r="E22" t="n">
-        <v>0.109</v>
+        <v>0.063</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="D23" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="E23" t="n">
-        <v>0.007999999999999998</v>
+        <v>0.013</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.197</v>
+        <v>-0.401</v>
       </c>
       <c r="D24" t="n">
-        <v>0.065</v>
+        <v>-0.037</v>
       </c>
       <c r="E24" t="n">
-        <v>0.132</v>
+        <v>0.364</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.077</v>
+        <v>0.041</v>
       </c>
       <c r="D25" t="n">
-        <v>0.03</v>
+        <v>0.038</v>
       </c>
       <c r="E25" t="n">
-        <v>0.047</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.032</v>
+        <v>0.077</v>
       </c>
       <c r="D26" t="n">
         <v>0.03</v>
       </c>
       <c r="E26" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.047</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.041</v>
+        <v>-0.066</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.012</v>
+        <v>-0.057</v>
       </c>
       <c r="E27" t="n">
-        <v>0.029</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.041</v>
+        <v>-0.041</v>
       </c>
       <c r="D28" t="n">
-        <v>0.038</v>
+        <v>-0.012</v>
       </c>
       <c r="E28" t="n">
-        <v>0.003000000000000003</v>
+        <v>0.029</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.066</v>
+        <v>0.022</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.057</v>
+        <v>0.014</v>
       </c>
       <c r="E29" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.007999999999999998</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.046</v>
+        <v>-0.054</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.002</v>
+        <v>-0.028</v>
       </c>
       <c r="E30" t="n">
-        <v>0.044</v>
+        <v>0.026</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.227</v>
+        <v>-0.019</v>
       </c>
       <c r="D31" t="n">
-        <v>0.021</v>
+        <v>-0.023</v>
       </c>
       <c r="E31" t="n">
-        <v>0.206</v>
+        <v>-0.004</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.019</v>
+        <v>-0.014</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.023</v>
+        <v>-0.003</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.004</v>
+        <v>0.011</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.005</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.008</v>
+        <v>-0.004</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -1494,16 +1494,16 @@
         <v>1.667057534699058</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1039364500786093</v>
+        <v>0.1039364500786116</v>
       </c>
       <c r="D2" t="n">
-        <v>1.463345835864039</v>
+        <v>1.463345835864034</v>
       </c>
       <c r="E2" t="n">
-        <v>1.870769233534078</v>
+        <v>1.870769233534082</v>
       </c>
       <c r="F2" t="n">
-        <v>6.802471999900441e-58</v>
+        <v>6.802471999941005e-58</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02459156738062897</v>
+        <v>-0.02459156738062896</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02140527432766425</v>
+        <v>0.02140527432766426</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06654513414205074</v>
+        <v>-0.06654513414205072</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01736199938079278</v>
+        <v>0.01736199938079281</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2506155650116347</v>
+        <v>0.2506155650116352</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1541,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.07551420708983098</v>
+        <v>-0.07551420708983096</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05280032846285382</v>
+        <v>0.05280032846285383</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1790009492489096</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02797253506924761</v>
+        <v>0.02797253506924764</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1526640960983818</v>
+        <v>0.152664096098382</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1566,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.07779512547504264</v>
+        <v>-0.07779512547504261</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0374586439619122</v>
+        <v>0.03745864396191226</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1512127185500993</v>
+        <v>-0.1512127185500994</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.004377532399985964</v>
+        <v>-0.004377532399985826</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03781752357803454</v>
+        <v>0.03781752357803488</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02905433458750126</v>
+        <v>0.02905433458750139</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03598413781957185</v>
+        <v>0.0359841378195719</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.04147327955358523</v>
+        <v>-0.0414732795535852</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09958194872858775</v>
+        <v>0.09958194872858797</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4194241955012069</v>
+        <v>0.4194241955012055</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1616,19 +1616,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02386878238742903</v>
+        <v>0.02386878238742904</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0344423072309577</v>
+        <v>0.03444230723095774</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.04363689932971155</v>
+        <v>-0.04363689932971161</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09137446410456962</v>
+        <v>0.09137446410456969</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4883047508165196</v>
+        <v>0.48830475081652</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1644,16 +1644,16 @@
         <v>0.03407929589427781</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03572350274317033</v>
+        <v>0.03572350274317036</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03593748288395385</v>
+        <v>-0.03593748288395392</v>
       </c>
       <c r="E8" t="n">
         <v>0.1040960746725095</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3400967596406816</v>
+        <v>0.3400967596406821</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03802463954938586</v>
+        <v>0.03802463954938589</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03434053922890853</v>
+        <v>0.03434053922890857</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.02928158054895975</v>
+        <v>-0.02928158054895979</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1053308596477315</v>
+        <v>0.1053308596477316</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2681722936342084</v>
+        <v>0.2681722936342085</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1691,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002108926766444226</v>
+        <v>0.002108926766444169</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05423092905058508</v>
+        <v>0.05423092905058527</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1041817410208495</v>
+        <v>-0.1041817410208499</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1083995945537379</v>
+        <v>0.1083995945537382</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9689797663112272</v>
+        <v>0.9689797663112281</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.00269831896369625</v>
+        <v>-0.002698318963696225</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05603185984561352</v>
+        <v>0.05603185984561369</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1125187462478948</v>
+        <v>-0.1125187462478951</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1071221083205023</v>
+        <v>0.1071221083205026</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9615912234151361</v>
+        <v>0.9615912234151366</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.09690684290742645</v>
+        <v>-0.09690684290742647</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05376611743977965</v>
+        <v>0.05376611743977976</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2022864966779455</v>
+        <v>-0.2022864966779457</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008472810863092567</v>
+        <v>0.008472810863092747</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0714860251902534</v>
+        <v>0.07148602519025385</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1769,16 +1769,16 @@
         <v>0.05861966677649851</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05290215792217611</v>
+        <v>0.05290215792217631</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.04506665745541698</v>
+        <v>-0.04506665745541735</v>
       </c>
       <c r="E13" t="n">
-        <v>0.162305991008414</v>
+        <v>0.1623059910084144</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2678285440445205</v>
+        <v>0.2678285440445223</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1791,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01179934497704018</v>
+        <v>0.01179934497704003</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05285544422806143</v>
+        <v>0.05285544422806162</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0917954220968257</v>
+        <v>-0.09179542209682622</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1153941120509061</v>
+        <v>0.1153941120509063</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8233502589464885</v>
+        <v>0.8233502589464913</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.08024560007397152</v>
+        <v>-0.08024560007397158</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05335929880103314</v>
+        <v>0.0533592988010333</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1848279039643078</v>
+        <v>-0.1848279039643081</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02433670381636471</v>
+        <v>0.02433670381636498</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1326141122249521</v>
+        <v>0.1326141122249531</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02846031488384167</v>
+        <v>0.0284603148838417</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05244704774958017</v>
+        <v>0.05244704774958041</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07433400980078794</v>
+        <v>-0.0743340098007884</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1312546395684713</v>
+        <v>0.1312546395684718</v>
       </c>
       <c r="F16" t="n">
-        <v>0.587371798496557</v>
+        <v>0.5873717984965583</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.00962293908780599</v>
+        <v>0.009622939087805975</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05256092363330955</v>
+        <v>0.05256092363330972</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09339457822764087</v>
+        <v>-0.09339457822764125</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1126404564032529</v>
+        <v>0.1126404564032532</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8547339765348229</v>
+        <v>0.8547339765348235</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1891,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09464919935341409</v>
+        <v>-0.09464919935341419</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05485507866520818</v>
+        <v>0.05485507866520829</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2021631779063336</v>
+        <v>-0.202163177906334</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01286477919950545</v>
+        <v>0.01286477919950557</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08444803584756586</v>
+        <v>0.08444803584756613</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03392408388401524</v>
+        <v>-0.03392408388401528</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05195030197739489</v>
+        <v>0.05195030197739511</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1357448047456892</v>
+        <v>-0.1357448047456896</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0678966369776587</v>
+        <v>0.06789663697765908</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5137496183866233</v>
+        <v>0.5137496183866246</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1944,16 +1944,16 @@
         <v>-0.02760797148779857</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05243884475714451</v>
+        <v>0.05243884475714469</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1303862186026888</v>
+        <v>-0.1303862186026892</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07517027562709169</v>
+        <v>0.07517027562709205</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5985551617146727</v>
+        <v>0.598555161714674</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1966,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05288647616397567</v>
+        <v>-0.05288647616397571</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05170437668208579</v>
+        <v>0.0517043766820859</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1542251923039564</v>
+        <v>-0.1542251923039566</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04845223997600506</v>
+        <v>0.04845223997600524</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3063727874189748</v>
+        <v>0.3063727874189753</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03821453321866508</v>
+        <v>-0.03821453321866491</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05200529590021591</v>
+        <v>0.05200529590021611</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1401430401884368</v>
+        <v>-0.140143040188437</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06371397375110663</v>
+        <v>0.06371397375110718</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4624491052692288</v>
+        <v>0.4624491052692326</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.05939396367195352</v>
+        <v>-0.05939396367195354</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05430017231427022</v>
+        <v>0.05430017231427046</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1658203457622421</v>
+        <v>-0.1658203457622426</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04703241841833507</v>
+        <v>0.04703241841833553</v>
       </c>
       <c r="F23" t="n">
-        <v>0.274039188317405</v>
+        <v>0.2740391883174071</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.00855425110000565</v>
+        <v>0.008554251100005588</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04714697844654477</v>
+        <v>0.04714697844654479</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.08385212863510828</v>
+        <v>-0.08385212863510838</v>
       </c>
       <c r="E24" t="n">
         <v>0.1009606308351196</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8560238336771215</v>
+        <v>0.8560238336771226</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2066,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.008330531317806207</v>
+        <v>0.00833053131780615</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02616718960488381</v>
+        <v>0.02616718960488387</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04295621788439694</v>
+        <v>-0.04295621788439712</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05961728052000936</v>
+        <v>0.05961728052000943</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7502134753562276</v>
+        <v>0.7502134753562298</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02424714499797272</v>
+        <v>0.02424714499797291</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03265065717218202</v>
+        <v>0.03265065717218204</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03974696713106844</v>
+        <v>-0.03974696713106829</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08824125712701388</v>
+        <v>0.08824125712701411</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4577096625377141</v>
+        <v>0.4577096625377107</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2116,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03912913997782919</v>
+        <v>-0.03912913997782914</v>
       </c>
       <c r="C27" t="n">
         <v>0.03172898075157672</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1013167995170842</v>
+        <v>-0.1013167995170841</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0230585195614258</v>
+        <v>0.02305851956142585</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2174898593271094</v>
+        <v>0.2174898593271098</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2141,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0192673475146302</v>
+        <v>0.01926734751463029</v>
       </c>
       <c r="C28" t="n">
         <v>0.03227922232167938</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.04399876568482276</v>
+        <v>-0.04399876568482267</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08253346071408317</v>
+        <v>0.08253346071408327</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5505766354403399</v>
+        <v>0.550576635440338</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.06728645489710119</v>
+        <v>0.06728645489710121</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03196900488547523</v>
+        <v>0.03196900488547524</v>
       </c>
       <c r="D29" t="n">
-        <v>0.004628356699984709</v>
+        <v>0.004628356699984695</v>
       </c>
       <c r="E29" t="n">
         <v>0.1299445530942177</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0353139150708292</v>
+        <v>0.03531391507082924</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0407159796972524</v>
+        <v>-0.04071597969725242</v>
       </c>
       <c r="C30" t="n">
         <v>0.04219485817141799</v>
@@ -2200,10 +2200,10 @@
         <v>-0.1234163820460073</v>
       </c>
       <c r="E30" t="n">
-        <v>0.04198442265150246</v>
+        <v>0.04198442265150243</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3345692469681958</v>
+        <v>0.3345692469681956</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2212,23 +2212,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.00336812727536743</v>
+        <v>-0.0009920422931855093</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001764528679284745</v>
+        <v>0.00157808271839598</v>
       </c>
       <c r="D31" t="n">
-        <v>-9.028538571869728e-05</v>
+        <v>-0.004085027585866694</v>
       </c>
       <c r="E31" t="n">
-        <v>0.006826539936453557</v>
+        <v>0.002100942999495675</v>
       </c>
       <c r="F31" t="n">
-        <v>0.05628826750555639</v>
+        <v>0.5295862719421283</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2237,23 +2237,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.065588116314736e-05</v>
+        <v>0.003368127275367437</v>
       </c>
       <c r="C32" t="n">
-        <v>0.004788074446685952</v>
+        <v>0.001764528679284745</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.009353797589637867</v>
+        <v>-9.028538571869207e-05</v>
       </c>
       <c r="E32" t="n">
-        <v>0.009415109351964161</v>
+        <v>0.006826539936453565</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9948915399209105</v>
+        <v>0.056288267505556</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2262,23 +2262,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4490720848345699</v>
+        <v>3.065588116314992e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01068359759505043</v>
+        <v>0.004788074446685941</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4281326183229523</v>
+        <v>-0.009353797589637841</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4700115513461875</v>
+        <v>0.009415109351964141</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.9948915399209101</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2287,23 +2287,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.001858686570725001</v>
+        <v>-0.028159565483449</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001577825229323158</v>
+        <v>0.02420948131337567</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.00123379405264704</v>
+        <v>-0.07560927694206077</v>
       </c>
       <c r="E34" t="n">
-        <v>0.004951167194097042</v>
+        <v>0.01929014597516276</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2387944710485399</v>
+        <v>0.2447634997487504</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2312,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.028159565483449</v>
+        <v>0.001858686570725002</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02420948131337568</v>
+        <v>0.001577825229323158</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.07560927694206077</v>
+        <v>-0.001233794052647039</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01929014597516278</v>
+        <v>0.004951167194097043</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2447634997487508</v>
+        <v>0.2387944710485393</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2337,23 +2337,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.00099204229318551</v>
+        <v>0.4490720848345699</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001578082718395978</v>
+        <v>0.01068359759505061</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.004085027585866692</v>
+        <v>0.428132618322952</v>
       </c>
       <c r="E36" t="n">
-        <v>0.002100942999495671</v>
+        <v>0.4700115513461878</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5295862719421276</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.713407322158421</v>
+        <v>-2.713407322158418</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5044376034036556</v>
+        <v>0.5044376034036603</v>
       </c>
       <c r="D2" t="n">
-        <v>7.486982883649802e-08</v>
+        <v>7.486982883652069e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2418,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02522051520904548</v>
+        <v>-0.02522051520904542</v>
       </c>
       <c r="C3" t="n">
         <v>0.1001657906734903</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8012051561485706</v>
+        <v>0.8012051561485711</v>
       </c>
     </row>
     <row r="4">
@@ -2434,13 +2434,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2243950733516431</v>
+        <v>0.2243950733516432</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2334051881144239</v>
+        <v>0.2334051881144238</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3363525367569156</v>
+        <v>0.336352536756915</v>
       </c>
     </row>
     <row r="5">
@@ -2453,10 +2453,10 @@
         <v>0.8152523591729706</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1732905987053342</v>
+        <v>0.1732905987053344</v>
       </c>
       <c r="D5" t="n">
-        <v>2.544403764026924e-06</v>
+        <v>2.544403764026986e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03529662509742201</v>
+        <v>0.03529662509742185</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1917359483069558</v>
+        <v>0.1917359483069561</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8539430379367479</v>
+        <v>0.8539430379367488</v>
       </c>
     </row>
     <row r="7">
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2770307728862447</v>
+        <v>0.2770307728862445</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1900876275228706</v>
+        <v>0.1900876275228709</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1450102574315855</v>
+        <v>0.1450102574315864</v>
       </c>
     </row>
     <row r="8">
@@ -2501,10 +2501,10 @@
         <v>0.103322246136425</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1951486965374491</v>
+        <v>0.1951486965374493</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5964905887803367</v>
+        <v>0.5964905887803371</v>
       </c>
     </row>
     <row r="9">
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8739030378849018</v>
+        <v>0.8739030378849016</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695379888770778</v>
+        <v>0.1695379888770781</v>
       </c>
       <c r="D9" t="n">
-        <v>2.541527320496774e-07</v>
+        <v>2.541527320496923e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04298175525170718</v>
+        <v>-0.04298175525170753</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2597533292652193</v>
+        <v>0.2597533292652202</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8685729341423559</v>
+        <v>0.8685729341423553</v>
       </c>
     </row>
     <row r="11">
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2734774183375253</v>
+        <v>-0.2734774183375255</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2785592488643227</v>
+        <v>0.2785592488643228</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3262197079678818</v>
+        <v>0.3262197079678817</v>
       </c>
     </row>
     <row r="12">
@@ -2562,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08217580196393745</v>
+        <v>0.08217580196393716</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2587287215011218</v>
+        <v>0.2587287215011221</v>
       </c>
       <c r="D12" t="n">
-        <v>0.750777935527874</v>
+        <v>0.7507779355278751</v>
       </c>
     </row>
     <row r="13">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03995788006654554</v>
+        <v>0.03995788006654508</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2568297818201679</v>
+        <v>0.2568297818201686</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8763631618417477</v>
+        <v>0.8763631618417494</v>
       </c>
     </row>
     <row r="14">
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05219347665548955</v>
+        <v>-0.05219347665548976</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2603443755509267</v>
+        <v>0.2603443755509273</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8411062907988998</v>
+        <v>0.8411062907988994</v>
       </c>
     </row>
     <row r="15">
@@ -2610,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1183975653249736</v>
+        <v>0.1183975653249733</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2570359266688491</v>
+        <v>0.2570359266688499</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6450665788994026</v>
+        <v>0.6450665788994044</v>
       </c>
     </row>
     <row r="16">
@@ -2626,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.002815011182393641</v>
+        <v>-0.00281501118239398</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2376522981116133</v>
+        <v>0.2376522981116134</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9905492122003419</v>
+        <v>0.9905492122003408</v>
       </c>
     </row>
     <row r="17">
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1056709152111887</v>
+        <v>0.1056709152111884</v>
       </c>
       <c r="C17" t="n">
         <v>0.2542906688395363</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6777380893434563</v>
+        <v>0.677738089343457</v>
       </c>
     </row>
     <row r="18">
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1371135645044835</v>
+        <v>-0.1371135645044839</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2634072330241222</v>
+        <v>0.2634072330241232</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6026884109023543</v>
+        <v>0.6026884109023545</v>
       </c>
     </row>
     <row r="19">
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02475228489410846</v>
+        <v>-0.02475228489410885</v>
       </c>
       <c r="C19" t="n">
         <v>0.2524092973060099</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9218814119969677</v>
+        <v>0.9218814119969665</v>
       </c>
     </row>
     <row r="20">
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07246351166486055</v>
+        <v>-0.07246351166486092</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2666987121614955</v>
+        <v>0.2666987121614957</v>
       </c>
       <c r="D20" t="n">
-        <v>0.785848458322072</v>
+        <v>0.785848458322071</v>
       </c>
     </row>
     <row r="21">
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2068090257965722</v>
+        <v>0.2068090257965718</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2439533267288634</v>
+        <v>0.2439533267288631</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3965827100652902</v>
+        <v>0.3965827100652906</v>
       </c>
     </row>
     <row r="22">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1686288808585493</v>
+        <v>-0.1686288808585498</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2694061394634706</v>
+        <v>0.2694061394634718</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5313620833011156</v>
+        <v>0.5313620833011161</v>
       </c>
     </row>
     <row r="23">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4997770753001366</v>
+        <v>-0.4997770753001369</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2864601345898811</v>
+        <v>0.2864601345898813</v>
       </c>
       <c r="D23" t="n">
         <v>0.08104313551548828</v>
@@ -2757,10 +2757,10 @@
         <v>0.9365913375115046</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1482811706186312</v>
+        <v>0.1482811706186313</v>
       </c>
       <c r="D24" t="n">
-        <v>2.678649464267732e-10</v>
+        <v>2.678649464267771e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5782787024565066</v>
+        <v>-0.5782787024565067</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1145314111910343</v>
+        <v>0.1145314111910344</v>
       </c>
       <c r="D25" t="n">
-        <v>4.439337879296617e-07</v>
+        <v>4.43933787929666e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2379613006187488</v>
+        <v>0.2379613006187487</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503209475356383</v>
+        <v>0.1503209475356384</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1134165507753402</v>
+        <v>0.1134165507753407</v>
       </c>
     </row>
     <row r="27">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04352683570925962</v>
+        <v>-0.04352683570925984</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1612096759797173</v>
+        <v>0.1612096759797175</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7871591884734994</v>
+        <v>0.7871591884734985</v>
       </c>
     </row>
     <row r="28">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07467572557157223</v>
+        <v>-0.07467572557157248</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1614290026159799</v>
+        <v>0.1614290026159801</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6436570199176109</v>
+        <v>0.6436570199176102</v>
       </c>
     </row>
     <row r="29">
@@ -2834,109 +2834,109 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09777326958921137</v>
+        <v>0.09777326958921112</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543602583723146</v>
+        <v>0.1543602583723147</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5264661972233927</v>
+        <v>0.5264661972233939</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.004998614827289044</v>
+        <v>-0.002450883409209257</v>
       </c>
       <c r="C30" t="n">
-        <v>0.008307994570919632</v>
+        <v>0.00712771118784129</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5473983322894256</v>
+        <v>0.7309569941465299</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.004172683243731375</v>
+        <v>-0.004998614827289062</v>
       </c>
       <c r="C31" t="n">
-        <v>0.02223526945739782</v>
+        <v>0.008307994570919656</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8511427450377156</v>
+        <v>0.5473983322894252</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01034291492939462</v>
+        <v>-0.004172683243731415</v>
       </c>
       <c r="C32" t="n">
-        <v>0.05138615505935841</v>
+        <v>0.0222352694573979</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8404810151443449</v>
+        <v>0.8511427450377147</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.006367932838418622</v>
+        <v>0.2275650381150179</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006881672701727245</v>
+        <v>0.1144549283876821</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3547856158497282</v>
+        <v>0.04678402178782448</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.227565038115018</v>
+        <v>0.006367932838418625</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1144549283876821</v>
+        <v>0.006881672701727249</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0467840217878245</v>
+        <v>0.3547856158497283</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.002450883409209247</v>
+        <v>0.01034291492939454</v>
       </c>
       <c r="C35" t="n">
-        <v>0.007127711187841274</v>
+        <v>0.05138615505935801</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7309569941465304</v>
+        <v>0.8404810151443449</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.001</v>
+        <v>0.059</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.002</v>
+        <v>0.021</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.096</v>
+        <v>-0.095</v>
       </c>
       <c r="D7" t="n">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="E7" t="n">
-        <v>0.078</v>
+        <v>0.09</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.059</v>
+        <v>0.033</v>
       </c>
       <c r="D8" t="n">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03799999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.007</v>
+        <v>-0.012</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.025</v>
+        <v>0.005</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.018</v>
+        <v>0.007</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.033</v>
+        <v>-0.054</v>
       </c>
       <c r="D10" t="n">
-        <v>0.025</v>
+        <v>-0.023</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008</v>
+        <v>0.031</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.014</v>
+        <v>0.007</v>
       </c>
       <c r="D12" t="n">
-        <v>0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0009999999999999992</v>
+        <v>0.002</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.044</v>
+        <v>0.185</v>
       </c>
       <c r="D13" t="n">
-        <v>0.026</v>
+        <v>0.015</v>
       </c>
       <c r="E13" t="n">
-        <v>0.018</v>
+        <v>0.17</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.181</v>
+        <v>-0.007</v>
       </c>
       <c r="D14" t="n">
-        <v>0.013</v>
+        <v>-0.025</v>
       </c>
       <c r="E14" t="n">
-        <v>0.168</v>
+        <v>-0.018</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.076</v>
+        <v>-0.09</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.002</v>
+        <v>-0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>0.074</v>
+        <v>0.06</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="D16" t="n">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="E16" t="n">
-        <v>0.006</v>
+        <v>-0.0009999999999999992</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.008</v>
+        <v>-0.096</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.007</v>
+        <v>0.018</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001</v>
+        <v>0.078</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.012</v>
+        <v>0.036</v>
       </c>
       <c r="D19" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.007</v>
+        <v>0.035</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.054</v>
+        <v>-0.008</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.023</v>
+        <v>-0.007</v>
       </c>
       <c r="E20" t="n">
-        <v>0.031</v>
+        <v>0.001</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.185</v>
+        <v>0.076</v>
       </c>
       <c r="D21" t="n">
-        <v>0.015</v>
+        <v>-0.002</v>
       </c>
       <c r="E21" t="n">
-        <v>0.17</v>
+        <v>0.074</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.215</v>
+        <v>0.075</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.059</v>
+        <v>0.005</v>
       </c>
       <c r="E22" t="n">
-        <v>0.156</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.095</v>
+        <v>0.044</v>
       </c>
       <c r="D24" t="n">
-        <v>0.005</v>
+        <v>0.026</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09</v>
+        <v>0.018</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.036</v>
+        <v>-0.015</v>
       </c>
       <c r="D26" t="n">
-        <v>0.001</v>
+        <v>-0.032</v>
       </c>
       <c r="E26" t="n">
-        <v>0.035</v>
+        <v>-0.017</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.075</v>
+        <v>-0.181</v>
       </c>
       <c r="D27" t="n">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.392</v>
+        <v>-0.215</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.028</v>
+        <v>-0.059</v>
       </c>
       <c r="E29" t="n">
-        <v>0.364</v>
+        <v>0.156</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.015</v>
+        <v>-0.001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.032</v>
+        <v>-0.002</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.017</v>
+        <v>-0.001</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.005</v>
+        <v>0.004</v>
       </c>
       <c r="E31" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.09</v>
+        <v>-0.392</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.03</v>
+        <v>-0.028</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06</v>
+        <v>0.364</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1388,16 +1388,16 @@
         <v>6217</v>
       </c>
       <c r="B2" t="n">
-        <v>6055.852863629239</v>
+        <v>6055.85286362924</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9954923524565367</v>
+        <v>0.9954923524565368</v>
       </c>
       <c r="D2" t="n">
         <v>0.1624039162238811</v>
       </c>
       <c r="E2" t="n">
-        <v>1.858123712730965</v>
+        <v>1.858123712730966</v>
       </c>
       <c r="F2" t="n">
         <v>1.149442947861497</v>
@@ -1467,16 +1467,16 @@
         <v>2.02836611587179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1142797777609083</v>
+        <v>0.1142797777609102</v>
       </c>
       <c r="D2" t="n">
-        <v>1.804381867299168</v>
+        <v>1.804381867299165</v>
       </c>
       <c r="E2" t="n">
-        <v>2.252350364444411</v>
+        <v>2.252350364444415</v>
       </c>
       <c r="F2" t="n">
-        <v>1.750587924743941e-70</v>
+        <v>1.750587924752775e-70</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.004454066658546854</v>
+        <v>-0.004454066658546853</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02264676650011666</v>
+        <v>0.02264676650011667</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04884091336506371</v>
+        <v>-0.04884091336506374</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03993278004797</v>
+        <v>0.03993278004797002</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8440813962195437</v>
+        <v>0.8440813962195438</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03389366488464311</v>
+        <v>-0.03389366488464319</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05785807270287898</v>
+        <v>0.05785807270287897</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1472934035971859</v>
+        <v>-0.147293403597186</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0795060738278997</v>
+        <v>0.07950607382789962</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5580052088357452</v>
+        <v>0.5580052088357441</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.006875661103275396</v>
+        <v>-0.0068756611032754</v>
       </c>
       <c r="C5" t="n">
         <v>0.03808494585975135</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08152078334154587</v>
+        <v>-0.08152078334154589</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06776946113499509</v>
+        <v>0.06776946113499507</v>
       </c>
       <c r="F5" t="n">
-        <v>0.856732674515668</v>
+        <v>0.8567326745156679</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001188297856113371</v>
+        <v>-0.001188297856112933</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0411998382811757</v>
+        <v>0.04119983828117571</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08193849705609235</v>
+        <v>-0.08193849705609194</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07956190134386562</v>
+        <v>0.07956190134386606</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9769903690159449</v>
+        <v>0.9769903690159534</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1592,16 +1592,16 @@
         <v>-0.06305858053336842</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0405900806393542</v>
+        <v>0.04059008063935422</v>
       </c>
       <c r="D7" t="n">
         <v>-0.1426136767160792</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01649651564934235</v>
+        <v>0.01649651564934239</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1202926126868604</v>
+        <v>0.1202926126868605</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1617,16 +1617,16 @@
         <v>-0.0650564428320632</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04132988827693285</v>
+        <v>0.04132988827693288</v>
       </c>
       <c r="D8" t="n">
         <v>-0.1460615353399158</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01594864967578936</v>
+        <v>0.01594864967578943</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1154695580659504</v>
+        <v>0.1154695580659507</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02905623760645398</v>
+        <v>-0.02905623760645399</v>
       </c>
       <c r="C9" t="n">
         <v>0.0394235410966261</v>
@@ -1648,10 +1648,10 @@
         <v>-0.1063249582988758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04821248308596788</v>
+        <v>0.04821248308596787</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4611055694915076</v>
+        <v>0.4611055694915073</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.06885067313730646</v>
+        <v>-0.06885067313730658</v>
       </c>
       <c r="C10" t="n">
         <v>0.06211585669370253</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1905955151258147</v>
+        <v>-0.1905955151258148</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05289416885120174</v>
+        <v>0.05289416885120161</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2676789754318667</v>
+        <v>0.2676789754318657</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1692,16 +1692,16 @@
         <v>-0.1221748468931794</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06092435583523097</v>
+        <v>0.06092435583523093</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2415843901115348</v>
+        <v>-0.2415843901115347</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.002765303674823999</v>
+        <v>-0.002765303674824054</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04492530998442441</v>
+        <v>0.04492530998442431</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.07838540326732421</v>
+        <v>-0.0783854032673242</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06092691482148856</v>
+        <v>0.06092691482148867</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1977999620065814</v>
+        <v>-0.1977999620065816</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04102915547193299</v>
+        <v>0.04102915547193323</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1982518618524621</v>
+        <v>0.1982518618524631</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.008522193482033581</v>
+        <v>0.008522193482033582</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05836873363374077</v>
+        <v>0.05836873363374081</v>
       </c>
       <c r="D13" t="n">
         <v>-0.1058784222633101</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1229228092273772</v>
+        <v>0.1229228092273773</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8839165415238849</v>
+        <v>0.883916541523885</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04039308737240788</v>
+        <v>-0.04039308737240796</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05674181331615584</v>
+        <v>0.05674181331615582</v>
       </c>
       <c r="D14" t="n">
         <v>-0.1516049978895686</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07081882314475282</v>
+        <v>0.0708188231447527</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4765420859642776</v>
+        <v>0.4765420859642767</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1792,16 +1792,16 @@
         <v>-0.1154125116566348</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06052942681222902</v>
+        <v>0.06052942681222905</v>
       </c>
       <c r="D15" t="n">
         <v>-0.2340480082134568</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003222984900187201</v>
+        <v>0.00322298490018727</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05655719180604712</v>
+        <v>0.05655719180604728</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1817,16 +1817,16 @@
         <v>-0.1015943982225829</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05923345190504559</v>
+        <v>0.05923345190504564</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2176898306364577</v>
+        <v>-0.2176898306364578</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01450103419129194</v>
+        <v>0.01450103419129202</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08631728613154406</v>
+        <v>0.08631728613154431</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.08898691774509294</v>
+        <v>-0.08898691774509293</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05739926877358286</v>
+        <v>0.05739926877358281</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2014874172802499</v>
+        <v>-0.2014874172802498</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02351358179006402</v>
+        <v>0.02351358179006394</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1210660526014484</v>
+        <v>0.1210660526014482</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.04535069185511181</v>
+        <v>-0.04535069185511201</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06190696804401327</v>
+        <v>0.06190696804401333</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1666861196134499</v>
+        <v>-0.1666861196134502</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07598473590322624</v>
+        <v>0.07598473590322613</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4638256196208014</v>
+        <v>0.4638256196207997</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.01255984200078624</v>
+        <v>-0.01255984200078625</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06121386203072943</v>
+        <v>0.06121386203072945</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1325368069356198</v>
+        <v>-0.1325368069356199</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1074171229340473</v>
+        <v>0.1074171229340474</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8374317271342939</v>
+        <v>0.8374317271342938</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06233504608425867</v>
+        <v>-0.06233504608425871</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06145398822825709</v>
+        <v>0.06145398822825716</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.182782649717991</v>
+        <v>-0.1827826497179912</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05811255754947368</v>
+        <v>0.05811255754947376</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3104220364751118</v>
+        <v>0.3104220364751119</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05962283374156475</v>
+        <v>-0.05962283374156474</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05902325596066306</v>
+        <v>0.05902325596066314</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1753062896747534</v>
+        <v>-0.1753062896747536</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05606062219162392</v>
+        <v>0.05606062219162408</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3124194392956611</v>
+        <v>0.3124194392956617</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.05042994771853605</v>
+        <v>-0.050429947718536</v>
       </c>
       <c r="C22" t="n">
         <v>0.06074201625882798</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1694821119341853</v>
+        <v>-0.1694821119341852</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06862221649711318</v>
+        <v>0.06862221649711323</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4064077928516452</v>
+        <v>0.4064077928516455</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06558214032641249</v>
+        <v>-0.06558214032641248</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05881748257355463</v>
+        <v>0.05881748257355475</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1808622878318918</v>
+        <v>-0.180862287831892</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04969800717906683</v>
+        <v>0.04969800717906708</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2648457060412739</v>
+        <v>0.2648457060412749</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.007941985483981985</v>
+        <v>0.007941985483981989</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05021926948700068</v>
+        <v>0.05021926948700065</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.09048597404045061</v>
+        <v>-0.09048597404045054</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1063699450084146</v>
+        <v>0.1063699450084145</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8743416143866745</v>
+        <v>0.8743416143866743</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2042,16 +2042,16 @@
         <v>0.04275887538360298</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0289953124189394</v>
+        <v>0.02899531241893932</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01407089267800519</v>
+        <v>-0.01407089267800504</v>
       </c>
       <c r="E25" t="n">
-        <v>0.09958864344521115</v>
+        <v>0.099588643445211</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1402979641274855</v>
+        <v>0.1402979641274845</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2067,16 +2067,16 @@
         <v>0.01702773825292613</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03628839344655835</v>
+        <v>0.03628839344655832</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05409620595914756</v>
+        <v>-0.05409620595914751</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08815168246499981</v>
+        <v>0.08815168246499976</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6389025774131478</v>
+        <v>0.6389025774131476</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04776265836687568</v>
+        <v>0.0477626583668756</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03631243242202282</v>
+        <v>0.03631243242202279</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.02340840137133361</v>
+        <v>-0.02340840137133364</v>
       </c>
       <c r="E27" t="n">
-        <v>0.118933718105085</v>
+        <v>0.1189337181050848</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1884006237939558</v>
+        <v>0.1884006237939562</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03849528892250782</v>
+        <v>0.03849528892250777</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03513724130562729</v>
+        <v>0.03513724130562726</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.03037243855261482</v>
+        <v>-0.0303724385526148</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1073630163976305</v>
+        <v>0.1073630163976304</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2732672273052895</v>
+        <v>0.2732672273052897</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005380707237649693</v>
+        <v>0.005380707237649666</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03555582911908339</v>
+        <v>0.03555582911908336</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06430743727621427</v>
+        <v>-0.06430743727621424</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07506885175151365</v>
+        <v>0.07506885175151357</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8797144375731928</v>
+        <v>0.8797144375731933</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.003320233432695046</v>
+        <v>-0.00332023343269494</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05015882681790457</v>
+        <v>0.0501588268179046</v>
       </c>
       <c r="D30" t="n">
         <v>-0.1016297275025698</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0949892606371797</v>
+        <v>0.09498926063717988</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9472230553604767</v>
+        <v>0.9472230553604785</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.001543895502937994</v>
+        <v>0.0002152465134243675</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001581102582020392</v>
+        <v>0.001692811914196195</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.004642799619561249</v>
+        <v>-0.003102603871000483</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001555008613685262</v>
+        <v>0.003533096897849218</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3288327776696814</v>
+        <v>0.898819116851622</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.009549274128434504</v>
+        <v>-0.001543895502937995</v>
       </c>
       <c r="C32" t="n">
-        <v>0.005236570244876897</v>
+        <v>0.001581102582020392</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.01981276321090731</v>
+        <v>-0.00464279961956125</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0007142149540383044</v>
+        <v>0.00155500861368526</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06821647769402407</v>
+        <v>0.328832777669681</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0003007900296359773</v>
+        <v>0.434691752414487</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001948498754003063</v>
+        <v>0.0122631678322901</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004119777411403151</v>
+        <v>0.4106563851268283</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003518197352131196</v>
+        <v>0.4587271197021457</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8773178945520058</v>
+        <v>3.233495669658714e-275</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.434691752414487</v>
+        <v>-0.009549274128434496</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01226316783229004</v>
+        <v>0.005236570244876901</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4106563851268284</v>
+        <v>-0.01981276321090731</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4587271197021456</v>
+        <v>0.0007142149540383218</v>
       </c>
       <c r="F34" t="n">
-        <v>3.233495669641422e-275</v>
+        <v>0.06821647769402457</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0002152465134243688</v>
+        <v>-0.0003007900296359825</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001692811914196195</v>
+        <v>0.001948498754003083</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.003102603871000482</v>
+        <v>-0.004119777411403195</v>
       </c>
       <c r="E35" t="n">
-        <v>0.003533096897849219</v>
+        <v>0.00351819735213123</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8988191168516214</v>
+        <v>0.8773178945520049</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.589409473419876</v>
+        <v>-2.589409473419878</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5031045718144744</v>
+        <v>0.503104571814456</v>
       </c>
       <c r="D2" t="n">
-        <v>2.648809631192281e-07</v>
+        <v>2.648809631189567e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04318498161254686</v>
+        <v>0.04318498161254691</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1065435099103228</v>
+        <v>0.1065435099103226</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6852370218892516</v>
+        <v>0.6852370218892512</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3414291668173601</v>
+        <v>0.34142916681736</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2253255698874616</v>
+        <v>0.2253255698874617</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1297039406487214</v>
+        <v>0.1297039406487218</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7562320294942515</v>
+        <v>0.7562320294942516</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1748738694459632</v>
+        <v>0.1748738694459631</v>
       </c>
       <c r="D5" t="n">
-        <v>1.529179373687517e-05</v>
+        <v>1.529179373687494e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2433,10 +2433,10 @@
         <v>0.1341634292941744</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1953208674076421</v>
+        <v>0.195320867407642</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4921537310985468</v>
+        <v>0.4921537310985465</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09566226402322772</v>
+        <v>-0.09566226402322769</v>
       </c>
       <c r="C8" t="n">
         <v>0.2104081937814554</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6493604462404063</v>
+        <v>0.6493604462404065</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.070551836763826</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1703735435645066</v>
+        <v>0.1703735435645067</v>
       </c>
       <c r="D9" t="n">
-        <v>3.309132456524803e-10</v>
+        <v>3.309132456524827e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09554047552828901</v>
+        <v>0.09554047552828877</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2825463042992082</v>
+        <v>0.2825463042992076</v>
       </c>
       <c r="D10" t="n">
-        <v>0.735256973094484</v>
+        <v>0.7352569730944842</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2120911081526139</v>
+        <v>0.2120911081526138</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2723979177423709</v>
+        <v>0.2723979177423699</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4362108592987917</v>
+        <v>0.4362108592987899</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2444325881052897</v>
+        <v>-0.2444325881052896</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3070429002527501</v>
+        <v>0.3070429002527494</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4259819868592517</v>
+        <v>0.4259819868592508</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2496062680064451</v>
+        <v>0.2496062680064452</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2703388739718409</v>
+        <v>0.2703388739718406</v>
       </c>
       <c r="D13" t="n">
-        <v>0.355846290351153</v>
+        <v>0.3558462903511522</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2898175614664937</v>
+        <v>0.2898175614664938</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2803190610071123</v>
+        <v>0.2803190610071128</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3011901132184961</v>
+        <v>0.3011901132184968</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.33982051665361</v>
+        <v>0.3398205166536103</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2686928948980221</v>
+        <v>0.2686928948980215</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2059727340404611</v>
+        <v>0.2059727340404597</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1269289753942507</v>
+        <v>0.1269289753942508</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2681297806792981</v>
+        <v>0.2681297806792982</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6359375739959069</v>
+        <v>0.6359375739959066</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1818641012766419</v>
+        <v>0.1818641012766422</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752098117728789</v>
+        <v>0.2752098117728785</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5087278635920078</v>
+        <v>0.5087278635920065</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3864469590948249</v>
+        <v>0.3864469590948251</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2676140000451041</v>
+        <v>0.2676140000451033</v>
       </c>
       <c r="D18" t="n">
-        <v>0.148726001844761</v>
+        <v>0.1487260018447597</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1244402747085721</v>
+        <v>0.1244402747085724</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2778369782669695</v>
+        <v>0.2778369782669692</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6542329221218897</v>
+        <v>0.6542329221218885</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2308101909230519</v>
+        <v>0.2308101909230522</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2780833406064973</v>
+        <v>0.278083340606496</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4065367134519948</v>
+        <v>0.4065367134519922</v>
       </c>
     </row>
     <row r="21">
@@ -2657,10 +2657,10 @@
         <v>0.2330335342161666</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673196819648366</v>
+        <v>0.2673196819648367</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3833496727885933</v>
+        <v>0.3833496727885934</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.05077438800389044</v>
+        <v>0.05077438800389069</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2847519964476458</v>
+        <v>0.2847519964476451</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8584788100921669</v>
+        <v>0.8584788100921659</v>
       </c>
     </row>
     <row r="23">
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01709893916197961</v>
+        <v>-0.01709893916197956</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925638244712276</v>
+        <v>0.2925638244712263</v>
       </c>
       <c r="D23" t="n">
         <v>0.9533940447535783</v>
@@ -2708,7 +2708,7 @@
         <v>0.1599839947303407</v>
       </c>
       <c r="D24" t="n">
-        <v>4.489744023837672e-08</v>
+        <v>4.489744023837721e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1383512112984198</v>
+        <v>-0.1383512112984199</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1508106992062234</v>
+        <v>0.1508106992062233</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3589418401519303</v>
+        <v>0.3589418401519298</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08371120214432402</v>
+        <v>-0.08371120214432409</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1573755377854196</v>
+        <v>0.1573755377854195</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5947813778609787</v>
+        <v>0.5947813778609781</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1111753607446195</v>
+        <v>-0.1111753607446196</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1482387657619015</v>
+        <v>0.1482387657619014</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4532697926760272</v>
+        <v>0.4532697926760266</v>
       </c>
     </row>
     <row r="29">
@@ -2788,87 +2788,87 @@
         <v>0.1545279196022677</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03920394898235115</v>
+        <v>0.03920394898235113</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.002589705940363017</v>
+        <v>0.01479837462877072</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007293744184584136</v>
+        <v>0.007085296655765525</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7225457586062486</v>
+        <v>0.03674343959712717</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01865810867195037</v>
+        <v>0.002589705940363016</v>
       </c>
       <c r="C31" t="n">
-        <v>0.02286606432621104</v>
+        <v>0.007293744184584129</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4145151389219862</v>
+        <v>0.7225457586062485</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0128665535497358</v>
+        <v>0.01704998181899492</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008184547747939351</v>
+        <v>0.04993149462297867</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1159379568009101</v>
+        <v>0.732751679791499</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01704998181899486</v>
+        <v>0.01865810867195039</v>
       </c>
       <c r="C33" t="n">
-        <v>0.04993149462297883</v>
+        <v>0.02286606432621099</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7327516797915008</v>
+        <v>0.4145151389219848</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01479837462877072</v>
+        <v>-0.01286655354973578</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007085296655765539</v>
+        <v>0.008184547747939126</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0367434395971276</v>
+        <v>0.1159379568009007</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.015</v>
+        <v>-0.392</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.032</v>
+        <v>-0.028</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.017</v>
+        <v>0.364</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.001</v>
+        <v>-0.181</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.008</v>
+        <v>0.013</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.007</v>
+        <v>0.168</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.013</v>
+        <v>0.059</v>
       </c>
       <c r="D8" t="n">
-        <v>0.006</v>
+        <v>0.021</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.351</v>
+        <v>-0.007</v>
       </c>
       <c r="D9" t="n">
-        <v>0.016</v>
+        <v>-0.025</v>
       </c>
       <c r="E9" t="n">
-        <v>0.335</v>
+        <v>-0.018</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.185</v>
+        <v>-0.215</v>
       </c>
       <c r="D10" t="n">
-        <v>0.015</v>
+        <v>-0.059</v>
       </c>
       <c r="E10" t="n">
-        <v>0.17</v>
+        <v>0.156</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.007</v>
+        <v>-0.015</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.025</v>
+        <v>-0.032</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.018</v>
+        <v>-0.017</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.181</v>
+        <v>-0.054</v>
       </c>
       <c r="D12" t="n">
-        <v>0.013</v>
+        <v>-0.023</v>
       </c>
       <c r="E12" t="n">
-        <v>0.168</v>
+        <v>0.031</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.054</v>
+        <v>0.036</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.023</v>
+        <v>0.001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.031</v>
+        <v>0.035</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.392</v>
+        <v>-0.001</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.028</v>
+        <v>-0.008</v>
       </c>
       <c r="E14" t="n">
-        <v>0.364</v>
+        <v>-0.007</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.007</v>
+        <v>0.033</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.005</v>
+        <v>0.025</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.036</v>
+        <v>-0.001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E16" t="n">
-        <v>0.035</v>
+        <v>-0.001</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.368</v>
+        <v>0.013</v>
       </c>
       <c r="D17" t="n">
         <v>0.006</v>
       </c>
       <c r="E17" t="n">
-        <v>0.362</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.059</v>
+        <v>0.01</v>
       </c>
       <c r="D18" t="n">
-        <v>0.021</v>
+        <v>0.004</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03799999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.215</v>
+        <v>0.014</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.059</v>
+        <v>0.015</v>
       </c>
       <c r="E19" t="n">
-        <v>0.156</v>
+        <v>-0.0009999999999999992</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.044</v>
+        <v>-0.095</v>
       </c>
       <c r="D20" t="n">
-        <v>0.026</v>
+        <v>0.005</v>
       </c>
       <c r="E20" t="n">
-        <v>0.018</v>
+        <v>0.09</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.008</v>
+        <v>0.368</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001</v>
+        <v>0.362</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.076</v>
+        <v>-0.096</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.002</v>
+        <v>0.018</v>
       </c>
       <c r="E22" t="n">
-        <v>0.074</v>
+        <v>0.078</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.095</v>
+        <v>-0.012</v>
       </c>
       <c r="D23" t="n">
         <v>0.005</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09</v>
+        <v>0.007</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.019</v>
+        <v>-0.09</v>
       </c>
       <c r="D24" t="n">
-        <v>0.007</v>
+        <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>0.012</v>
+        <v>0.06</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.096</v>
+        <v>-0.008</v>
       </c>
       <c r="D25" t="n">
-        <v>0.018</v>
+        <v>-0.007</v>
       </c>
       <c r="E25" t="n">
-        <v>0.078</v>
+        <v>0.001</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01</v>
+        <v>-0.019</v>
       </c>
       <c r="D26" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="E26" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.075</v>
+        <v>0.351</v>
       </c>
       <c r="D28" t="n">
-        <v>0.005</v>
+        <v>0.016</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.335</v>
       </c>
       <c r="F28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.014</v>
+        <v>0.075</v>
       </c>
       <c r="D29" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0009999999999999992</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.033</v>
+        <v>0.044</v>
       </c>
       <c r="D30" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="E30" t="n">
-        <v>0.008</v>
+        <v>0.018</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.012</v>
+        <v>0.185</v>
       </c>
       <c r="D31" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="E31" t="n">
-        <v>0.007</v>
+        <v>0.17</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.09</v>
+        <v>0.076</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.03</v>
+        <v>-0.002</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06</v>
+        <v>0.074</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.181</v>
+        <v>-0.392</v>
       </c>
       <c r="D6" t="n">
-        <v>0.013</v>
+        <v>-0.028</v>
       </c>
       <c r="E6" t="n">
-        <v>0.168</v>
+        <v>0.364</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01</v>
+        <v>-0.181</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006</v>
+        <v>0.168</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.076</v>
+        <v>0.044</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.002</v>
+        <v>0.026</v>
       </c>
       <c r="E8" t="n">
-        <v>0.074</v>
+        <v>0.018</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.095</v>
+        <v>0.351</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005</v>
+        <v>0.016</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09</v>
+        <v>0.335</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.008</v>
+        <v>0.014</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.007</v>
+        <v>0.015</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001</v>
+        <v>-0.0009999999999999992</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.392</v>
+        <v>-0.095</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.028</v>
+        <v>0.005</v>
       </c>
       <c r="E11" t="n">
-        <v>0.364</v>
+        <v>0.09</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.001</v>
+        <v>-0.215</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.002</v>
+        <v>-0.059</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.001</v>
+        <v>0.156</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="D13" t="n">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0009999999999999992</v>
+        <v>0.006</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.059</v>
+        <v>0.076</v>
       </c>
       <c r="D14" t="n">
-        <v>0.021</v>
+        <v>-0.002</v>
       </c>
       <c r="E14" t="n">
-        <v>0.03799999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.033</v>
+        <v>0.368</v>
       </c>
       <c r="D15" t="n">
-        <v>0.025</v>
+        <v>0.006</v>
       </c>
       <c r="E15" t="n">
-        <v>0.008</v>
+        <v>0.362</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.007</v>
+        <v>-0.001</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.036</v>
+        <v>-0.001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.001</v>
+        <v>-0.008</v>
       </c>
       <c r="E17" t="n">
-        <v>0.035</v>
+        <v>-0.007</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.015</v>
+        <v>0.013</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.032</v>
+        <v>0.006</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.017</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.096</v>
+        <v>0.007</v>
       </c>
       <c r="D19" t="n">
-        <v>0.018</v>
+        <v>-0.005</v>
       </c>
       <c r="E19" t="n">
-        <v>0.078</v>
+        <v>0.002</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.001</v>
+        <v>-0.054</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.008</v>
+        <v>-0.023</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.007</v>
+        <v>0.031</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="D21" t="n">
         <v>-0.007</v>
       </c>
-      <c r="D21" t="n">
-        <v>-0.025</v>
-      </c>
       <c r="E21" t="n">
-        <v>-0.018</v>
+        <v>0.001</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.075</v>
+        <v>0.185</v>
       </c>
       <c r="D22" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.019</v>
+        <v>0.059</v>
       </c>
       <c r="D23" t="n">
-        <v>0.007</v>
+        <v>0.021</v>
       </c>
       <c r="E23" t="n">
-        <v>0.012</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.351</v>
+        <v>-0.09</v>
       </c>
       <c r="D24" t="n">
-        <v>0.016</v>
+        <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>0.335</v>
+        <v>0.06</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.054</v>
+        <v>0.033</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.023</v>
+        <v>0.025</v>
       </c>
       <c r="E25" t="n">
-        <v>0.031</v>
+        <v>0.008</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.09</v>
+        <v>0.036</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03</v>
+        <v>0.001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06</v>
+        <v>0.035</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.368</v>
+        <v>0.075</v>
       </c>
       <c r="D28" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="E28" t="n">
-        <v>0.362</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.013</v>
+        <v>-0.019</v>
       </c>
       <c r="D29" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="E29" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.215</v>
+        <v>-0.015</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.059</v>
+        <v>-0.032</v>
       </c>
       <c r="E30" t="n">
-        <v>0.156</v>
+        <v>-0.017</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.185</v>
+        <v>-0.096</v>
       </c>
       <c r="D31" t="n">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="E31" t="n">
-        <v>0.17</v>
+        <v>0.078</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.044</v>
+        <v>-0.007</v>
       </c>
       <c r="D32" t="n">
-        <v>0.026</v>
+        <v>-0.025</v>
       </c>
       <c r="E32" t="n">
-        <v>0.018</v>
+        <v>-0.018</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1397,7 +1397,7 @@
         <v>0.1624039162238811</v>
       </c>
       <c r="E2" t="n">
-        <v>1.858123712730965</v>
+        <v>1.858123712730966</v>
       </c>
       <c r="F2" t="n">
         <v>1.149442947861497</v>
@@ -1467,16 +1467,16 @@
         <v>2.02836611587179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1142797777609051</v>
+        <v>0.114279777760911</v>
       </c>
       <c r="D2" t="n">
-        <v>1.804381867299175</v>
+        <v>1.804381867299163</v>
       </c>
       <c r="E2" t="n">
-        <v>2.252350364444406</v>
+        <v>2.252350364444417</v>
       </c>
       <c r="F2" t="n">
-        <v>1.750587924728219e-70</v>
+        <v>1.750587924756419e-70</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.004454066658546868</v>
+        <v>-0.004454066658546861</v>
       </c>
       <c r="C3" t="n">
         <v>0.02264676650011666</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04884091336506374</v>
+        <v>-0.04884091336506372</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03993278004797</v>
+        <v>0.03993278004796999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8440813962195433</v>
+        <v>0.8440813962195435</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03389366488464316</v>
+        <v>-0.03389366488464311</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05785807270287898</v>
+        <v>0.05785807270287897</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.147293403597186</v>
+        <v>-0.1472934035971859</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07950607382789965</v>
+        <v>0.0795060738278997</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5580052088357446</v>
+        <v>0.5580052088357452</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.006875661103275406</v>
+        <v>-0.006875661103275434</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03808494585975132</v>
+        <v>0.03808494585975136</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08152078334154585</v>
+        <v>-0.08152078334154593</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06776946113499503</v>
+        <v>0.06776946113499506</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8567326745156677</v>
+        <v>0.8567326745156673</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001188297856113079</v>
+        <v>-0.001188297856113121</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0411998382811757</v>
+        <v>0.04119983828117572</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08193849705609205</v>
+        <v>-0.08193849705609213</v>
       </c>
       <c r="E6" t="n">
         <v>0.0795619013438659</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9769903690159506</v>
+        <v>0.9769903690159498</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1592,16 +1592,16 @@
         <v>-0.06305858053336844</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0405900806393542</v>
+        <v>0.04059008063935423</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1426136767160792</v>
+        <v>-0.1426136767160793</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01649651564934233</v>
+        <v>0.01649651564934239</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1202926126868602</v>
+        <v>0.1202926126868605</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06505644283206324</v>
+        <v>-0.06505644283206323</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04132988827693283</v>
+        <v>0.04132988827693287</v>
       </c>
       <c r="D8" t="n">
         <v>-0.1460615353399158</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01594864967578929</v>
+        <v>0.01594864967578938</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1154695580659501</v>
+        <v>0.1154695580659504</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02905623760645398</v>
+        <v>-0.029056237606454</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03942354109662608</v>
+        <v>0.03942354109662611</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1063249582988758</v>
+        <v>-0.1063249582988759</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04821248308596785</v>
+        <v>0.04821248308596788</v>
       </c>
       <c r="F9" t="n">
         <v>0.4611055694915073</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.06885067313730664</v>
+        <v>-0.06885067313730643</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0621158566937024</v>
+        <v>0.06211585669370266</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1905955151258146</v>
+        <v>-0.1905955151258149</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0528941688512013</v>
+        <v>0.05289416885120203</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2676789754318643</v>
+        <v>0.2676789754318678</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1221748468931795</v>
+        <v>-0.1221748468931794</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06092435583523084</v>
+        <v>0.06092435583523104</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2415843901115346</v>
+        <v>-0.2415843901115349</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.002765303674824346</v>
+        <v>-0.002765303674823832</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04492530998442382</v>
+        <v>0.04492530998442472</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.07838540326732434</v>
+        <v>-0.07838540326732418</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06092691482148845</v>
+        <v>0.06092691482148872</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1977999620065813</v>
+        <v>-0.1977999620065817</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04102915547193263</v>
+        <v>0.04102915547193332</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1982518618524606</v>
+        <v>0.1982518618524636</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.008522193482033499</v>
+        <v>0.008522193482033593</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05836873363374073</v>
+        <v>0.05836873363374082</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.10587842226331</v>
+        <v>-0.1058784222633101</v>
       </c>
       <c r="E13" t="n">
-        <v>0.122922809227377</v>
+        <v>0.1229228092273773</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8839165415238859</v>
+        <v>0.8839165415238849</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04039308737240806</v>
+        <v>-0.04039308737240774</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05674181331615572</v>
+        <v>0.05674181331615595</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1516049978895685</v>
+        <v>-0.1516049978895687</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07081882314475241</v>
+        <v>0.07081882314475317</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4765420859642748</v>
+        <v>0.4765420859642803</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1154125116566349</v>
+        <v>-0.1154125116566348</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06052942681222889</v>
+        <v>0.0605294268122291</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2340480082134566</v>
+        <v>-0.2340480082134569</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00322298490018684</v>
+        <v>0.003222984900187381</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05655719180604638</v>
+        <v>0.05655719180604749</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.101594398222583</v>
+        <v>-0.1015943982225829</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05923345190504544</v>
+        <v>0.05923345190504568</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2176898306364575</v>
+        <v>-0.2176898306364579</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01450103419129155</v>
+        <v>0.0145010341912921</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08631728613154301</v>
+        <v>0.08631728613154455</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.08898691774509301</v>
+        <v>-0.08898691774509293</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05739926877358271</v>
+        <v>0.05739926877358301</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2014874172802497</v>
+        <v>-0.2014874172802502</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02351358179006366</v>
+        <v>0.02351358179006434</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1210660526014472</v>
+        <v>0.1210660526014495</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.04535069185511199</v>
+        <v>-0.04535069185511181</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06190696804401315</v>
+        <v>0.0619069680440134</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1666861196134498</v>
+        <v>-0.1666861196134501</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07598473590322583</v>
+        <v>0.07598473590322649</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4638256196207988</v>
+        <v>0.4638256196208023</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0125598420007864</v>
+        <v>-0.01255984200078624</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06121386203072923</v>
+        <v>0.06121386203072944</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1325368069356196</v>
+        <v>-0.1325368069356198</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1074171229340468</v>
+        <v>0.1074171229340474</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8374317271342915</v>
+        <v>0.837431727134294</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06233504608425883</v>
+        <v>-0.06233504608425865</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06145398822825695</v>
+        <v>0.06145398822825722</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1827826497179909</v>
+        <v>-0.1827826497179912</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05811255754947324</v>
+        <v>0.05811255754947394</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3104220364751094</v>
+        <v>0.3104220364751129</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05962283374156484</v>
+        <v>-0.05962283374156472</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05902325596066291</v>
+        <v>0.05902325596066312</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1753062896747532</v>
+        <v>-0.1753062896747535</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05606062219162353</v>
+        <v>0.05606062219162408</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3124194392956592</v>
+        <v>0.312419439295662</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.05042994771853613</v>
+        <v>-0.05042994771853593</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06074201625882784</v>
+        <v>0.06074201625882798</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1694821119341851</v>
+        <v>-0.1694821119341852</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06862221649711284</v>
+        <v>0.06862221649711331</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4064077928516434</v>
+        <v>0.4064077928516462</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06558214032641259</v>
+        <v>-0.06558214032641245</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05881748257355448</v>
+        <v>0.05881748257355469</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1808622878318916</v>
+        <v>-0.1808622878318919</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04969800717906644</v>
+        <v>0.04969800717906699</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2648457060412719</v>
+        <v>0.2648457060412744</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.007941985483981975</v>
+        <v>0.007941985483982004</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05021926948700063</v>
+        <v>0.05021926948700065</v>
       </c>
       <c r="D24" t="n">
         <v>-0.09048597404045053</v>
@@ -2026,7 +2026,7 @@
         <v>0.1063699450084145</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8743416143866746</v>
+        <v>0.8743416143866741</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04275887538360296</v>
+        <v>0.04275887538360294</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02899531241893926</v>
+        <v>0.02899531241893934</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01407089267800495</v>
+        <v>-0.01407089267800513</v>
       </c>
       <c r="E25" t="n">
-        <v>0.09958864344521087</v>
+        <v>0.099588643445211</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1402979641274837</v>
+        <v>0.1402979641274852</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01702773825292614</v>
+        <v>0.01702773825292602</v>
       </c>
       <c r="C26" t="n">
         <v>0.03628839344655835</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05409620595914756</v>
+        <v>-0.05409620595914766</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08815168246499984</v>
+        <v>0.08815168246499971</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6389025774131476</v>
+        <v>0.6389025774131499</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04776265836687571</v>
+        <v>0.04776265836687561</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03631243242202281</v>
+        <v>0.03631243242202283</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.02340840137133357</v>
+        <v>-0.0234084013713337</v>
       </c>
       <c r="E27" t="n">
-        <v>0.118933718105085</v>
+        <v>0.1189337181050849</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1884006237939555</v>
+        <v>0.1884006237939565</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03849528892250782</v>
+        <v>0.0384952889225078</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0351372413056273</v>
+        <v>0.03513724130562731</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.03037243855261483</v>
+        <v>-0.03037243855261488</v>
       </c>
       <c r="E28" t="n">
         <v>0.1073630163976305</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2732672273052895</v>
+        <v>0.27326722730529</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005380707237649681</v>
+        <v>0.005380707237649678</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03555582911908339</v>
+        <v>0.03555582911908342</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0643074372762143</v>
+        <v>-0.06430743727621435</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07506885175151365</v>
+        <v>0.0750688517515137</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8797144375731931</v>
+        <v>0.8797144375731932</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.003320233432694951</v>
+        <v>-0.003320233432694986</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05015882681790457</v>
+        <v>0.05015882681790459</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1016297275025697</v>
+        <v>-0.1016297275025698</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0949892606371798</v>
+        <v>0.09498926063717981</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9472230553604782</v>
+        <v>0.9472230553604777</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.000215246513424368</v>
+        <v>0.0002152465134243671</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001692811914196193</v>
+        <v>0.001692811914196198</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.003102603871000477</v>
+        <v>-0.00310260387100049</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003533096897849214</v>
+        <v>0.003533096897849224</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8988191168516216</v>
+        <v>0.8988191168516224</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0003007900296359918</v>
+        <v>-0.0003007900296359844</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001948498754003041</v>
+        <v>0.001948498754003064</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004119777411403122</v>
+        <v>-0.00411977741140316</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003518197352131138</v>
+        <v>0.003518197352131191</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8773178945519985</v>
+        <v>0.8773178945520029</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4346917524144869</v>
+        <v>-0.001543895502937994</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01226316783229004</v>
+        <v>0.001581102582020392</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4106563851268283</v>
+        <v>-0.004642799619561249</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4587271197021455</v>
+        <v>0.001555008613685261</v>
       </c>
       <c r="F33" t="n">
-        <v>3.233495669640318e-275</v>
+        <v>0.3288327776696812</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.001543895502937996</v>
+        <v>0.434691752414487</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001581102582020384</v>
+        <v>0.01226316783229007</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004642799619561235</v>
+        <v>0.4106563851268283</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001555008613685243</v>
+        <v>0.4587271197021456</v>
       </c>
       <c r="F34" t="n">
-        <v>0.328832777669678</v>
+        <v>3.233495669649517e-275</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.009549274128434511</v>
+        <v>-0.009549274128434503</v>
       </c>
       <c r="C35" t="n">
-        <v>0.005236570244876912</v>
+        <v>0.005236570244876946</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.01981276321090735</v>
+        <v>-0.01981276321090741</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0007142149540383287</v>
+        <v>0.0007142149540384033</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0682164776940247</v>
+        <v>0.06821647769402675</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.589409473419876</v>
+        <v>-2.589409473419878</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5031045718144668</v>
+        <v>0.5031045718144701</v>
       </c>
       <c r="D2" t="n">
-        <v>2.648809631191155e-07</v>
+        <v>2.648809631191609e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04318498161254683</v>
+        <v>0.04318498161254685</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1065435099103227</v>
+        <v>0.1065435099103228</v>
       </c>
       <c r="D3" t="n">
         <v>0.6852370218892518</v>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3414291668173602</v>
+        <v>0.3414291668173601</v>
       </c>
       <c r="C4" t="n">
         <v>0.2253255698874617</v>
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7562320294942516</v>
+        <v>0.7562320294942515</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1748738694459632</v>
+        <v>0.1748738694459635</v>
       </c>
       <c r="D5" t="n">
-        <v>1.529179373687506e-05</v>
+        <v>1.529179373687554e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2417,10 +2417,10 @@
         <v>-0.1784790633221359</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2136767975499138</v>
+        <v>0.2136767975499141</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4035624257334062</v>
+        <v>0.4035624257334068</v>
       </c>
     </row>
     <row r="7">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1341634292941744</v>
+        <v>0.1341634292941743</v>
       </c>
       <c r="C7" t="n">
-        <v>0.195320867407642</v>
+        <v>0.1953208674076423</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4921537310985463</v>
+        <v>0.4921537310985474</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09566226402322774</v>
+        <v>-0.09566226402322769</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2104081937814555</v>
+        <v>0.2104081937814556</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6493604462404066</v>
+        <v>0.6493604462404068</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.070551836763826</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1703735435645067</v>
+        <v>0.1703735435645069</v>
       </c>
       <c r="D9" t="n">
-        <v>3.309132456524852e-10</v>
+        <v>3.309132456524996e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09554047552828922</v>
+        <v>0.09554047552828926</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2825463042992085</v>
+        <v>0.2825463042992097</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7352569730944838</v>
+        <v>0.7352569730944847</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2120911081526143</v>
+        <v>0.2120911081526142</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2723979177423709</v>
+        <v>0.2723979177423718</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4362108592987908</v>
+        <v>0.4362108592987923</v>
       </c>
     </row>
     <row r="12">
@@ -2513,10 +2513,10 @@
         <v>-0.2444325881052893</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3070429002527503</v>
+        <v>0.3070429002527506</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4259819868592527</v>
+        <v>0.425981986859253</v>
       </c>
     </row>
     <row r="13">
@@ -2529,10 +2529,10 @@
         <v>0.2496062680064456</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2703388739718406</v>
+        <v>0.2703388739718417</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3558462903511516</v>
+        <v>0.3558462903511534</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.289817561466494</v>
+        <v>0.2898175614664941</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2803190610071128</v>
+        <v>0.2803190610071132</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3011901132184963</v>
+        <v>0.301190113218497</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3398205166536108</v>
+        <v>0.3398205166536106</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2686928948980217</v>
+        <v>0.2686928948980226</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2059727340404595</v>
+        <v>0.2059727340404611</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1269289753942511</v>
+        <v>0.1269289753942512</v>
       </c>
       <c r="C16" t="n">
-        <v>0.268129780679298</v>
+        <v>0.2681297806792991</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6359375739959057</v>
+        <v>0.6359375739959066</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1818641012766426</v>
+        <v>0.1818641012766424</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752098117728786</v>
+        <v>0.2752098117728798</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5087278635920056</v>
+        <v>0.5087278635920081</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3864469590948256</v>
+        <v>0.3864469590948255</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2676140000451047</v>
+        <v>0.2676140000451039</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1487260018447613</v>
+        <v>0.1487260018447602</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1244402747085727</v>
+        <v>0.1244402747085726</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2778369782669697</v>
+        <v>0.2778369782669702</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6542329221218884</v>
+        <v>0.6542329221218893</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2308101909230525</v>
+        <v>0.2308101909230524</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2780833406064971</v>
+        <v>0.2780833406064979</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4065367134519935</v>
+        <v>0.4065367134519948</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2330335342161671</v>
+        <v>0.233033534216167</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673196819648361</v>
+        <v>0.2673196819648372</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3833496727885913</v>
+        <v>0.3833496727885936</v>
       </c>
     </row>
     <row r="22">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.05077438800389093</v>
+        <v>0.0507743880038909</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2847519964476465</v>
+        <v>0.2847519964476463</v>
       </c>
       <c r="D22" t="n">
         <v>0.8584788100921659</v>
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01709893916197908</v>
+        <v>-0.01709893916197914</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925638244712272</v>
+        <v>0.2925638244712279</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9533940447535797</v>
+        <v>0.9533940447535796</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8751793875051906</v>
+        <v>0.8751793875051905</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1599839947303407</v>
+        <v>0.1599839947303408</v>
       </c>
       <c r="D24" t="n">
-        <v>4.489744023837706e-08</v>
+        <v>4.489744023837755e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5929479835845773</v>
+        <v>-0.5929479835845772</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1169096769872892</v>
+        <v>0.1169096769872894</v>
       </c>
       <c r="D25" t="n">
-        <v>3.93973281587656e-07</v>
+        <v>3.939732815876743e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1383512112984201</v>
+        <v>-0.1383512112984197</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1508106992062234</v>
+        <v>0.1508106992062235</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3589418401519292</v>
+        <v>0.3589418401519312</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08371120214432426</v>
+        <v>-0.08371120214432404</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1573755377854195</v>
+        <v>0.1573755377854197</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5947813778609774</v>
+        <v>0.5947813778609787</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1111753607446199</v>
+        <v>-0.1111753607446195</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1482387657619016</v>
+        <v>0.1482387657619015</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4532697926760261</v>
+        <v>0.4532697926760273</v>
       </c>
     </row>
     <row r="29">
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3186427171078561</v>
+        <v>-0.3186427171078558</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1545279196022679</v>
+        <v>0.1545279196022678</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03920394898235129</v>
+        <v>0.03920394898235136</v>
       </c>
     </row>
     <row r="30">
@@ -2801,10 +2801,10 @@
         <v>0.01479837462877072</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00708529665576556</v>
+        <v>0.007085296655765553</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03674343959712813</v>
+        <v>0.03674343959712793</v>
       </c>
     </row>
     <row r="31">
@@ -2814,45 +2814,45 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0128665535497358</v>
+        <v>-0.01286655354973579</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008184547747939246</v>
+        <v>0.008184547747939069</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1159379568009055</v>
+        <v>0.1159379568008977</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01704998181899479</v>
+        <v>0.002589705940363016</v>
       </c>
       <c r="C32" t="n">
-        <v>0.04993149462297924</v>
+        <v>0.007293744184584179</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7327516797915039</v>
+        <v>0.7225457586062503</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.00258970594036301</v>
+        <v>0.01704998181899492</v>
       </c>
       <c r="C33" t="n">
-        <v>0.007293744184584137</v>
+        <v>0.04993149462297874</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7225457586062494</v>
+        <v>0.7327516797914995</v>
       </c>
     </row>
     <row r="34">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01865810867195037</v>
+        <v>0.0186581086719504</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02286606432621126</v>
+        <v>0.02286606432621106</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4145151389219907</v>
+        <v>0.4145151389219861</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.024</v>
+        <v>-0.082</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004</v>
+        <v>-0.028</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.369</v>
+        <v>0.045</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="E7" t="n">
-        <v>0.36</v>
+        <v>0.038</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.388</v>
+        <v>-0.008</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03</v>
+        <v>-0.018</v>
       </c>
       <c r="E8" t="n">
-        <v>0.358</v>
+        <v>-0.009999999999999998</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.003</v>
+        <v>-0.031</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001</v>
+        <v>-0.005</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002</v>
+        <v>0.026</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.036</v>
+        <v>-0.117</v>
       </c>
       <c r="D10" t="n">
-        <v>0.008</v>
+        <v>-0.004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.028</v>
+        <v>0.113</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.095</v>
+        <v>0.19</v>
       </c>
       <c r="D11" t="n">
-        <v>0.015</v>
+        <v>0.025</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08</v>
+        <v>0.165</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.008</v>
+        <v>-0.183</v>
       </c>
       <c r="D12" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002</v>
+        <v>0.174</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.082</v>
+        <v>0.011</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.028</v>
+        <v>0.003</v>
       </c>
       <c r="E13" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.008</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="D14" t="n">
-        <v>0.022</v>
+        <v>0.008</v>
       </c>
       <c r="E14" t="n">
-        <v>0.013</v>
+        <v>0.028</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.183</v>
+        <v>0.003</v>
       </c>
       <c r="D15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.174</v>
+        <v>0.002</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.216</v>
+        <v>0.075</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.059</v>
+        <v>0.005</v>
       </c>
       <c r="E16" t="n">
-        <v>0.157</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.011</v>
+        <v>-0.018</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="E17" t="n">
-        <v>0.008</v>
+        <v>0.013</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.015</v>
+        <v>0.015</v>
       </c>
       <c r="D18" t="n">
-        <v>0.002</v>
+        <v>0.017</v>
       </c>
       <c r="E18" t="n">
-        <v>0.013</v>
+        <v>-0.002000000000000002</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.015</v>
+        <v>0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.026</v>
+        <v>0.006</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.011</v>
+        <v>0.002</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.117</v>
+        <v>0.35</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.004</v>
+        <v>0.018</v>
       </c>
       <c r="E20" t="n">
-        <v>0.113</v>
+        <v>0.332</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.045</v>
+        <v>0.369</v>
       </c>
       <c r="D21" t="n">
-        <v>0.007</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.038</v>
+        <v>0.36</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.031</v>
+        <v>-0.388</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.005</v>
+        <v>-0.03</v>
       </c>
       <c r="E23" t="n">
-        <v>0.026</v>
+        <v>0.358</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.075</v>
+        <v>-0.015</v>
       </c>
       <c r="D24" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.008</v>
+        <v>-0.216</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.018</v>
+        <v>-0.059</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.009999999999999998</v>
+        <v>0.157</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.099</v>
+        <v>0.024</v>
       </c>
       <c r="D26" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="D27" t="n">
-        <v>0.003</v>
+        <v>0.022</v>
       </c>
       <c r="E27" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.19</v>
+        <v>0.036</v>
       </c>
       <c r="D28" t="n">
-        <v>0.025</v>
+        <v>0.019</v>
       </c>
       <c r="E28" t="n">
-        <v>0.165</v>
+        <v>0.017</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.018</v>
+        <v>-0.015</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005</v>
+        <v>-0.026</v>
       </c>
       <c r="E29" t="n">
-        <v>0.013</v>
+        <v>-0.011</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.35</v>
+        <v>0.099</v>
       </c>
       <c r="D30" t="n">
-        <v>0.018</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.332</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>-0.095</v>
+      </c>
+      <c r="D31" t="n">
         <v>0.015</v>
       </c>
-      <c r="D31" t="n">
-        <v>0.017</v>
-      </c>
       <c r="E31" t="n">
-        <v>-0.002000000000000002</v>
+        <v>0.08</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.036</v>
+        <v>0.02</v>
       </c>
       <c r="D32" t="n">
-        <v>0.019</v>
+        <v>0.003</v>
       </c>
       <c r="E32" t="n">
         <v>0.017</v>
@@ -1403,7 +1403,7 @@
         <v>1.165474339027959</v>
       </c>
       <c r="G2" t="n">
-        <v>1.856659647949908</v>
+        <v>1.856659647949909</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.916286644504689</v>
+        <v>1.91628664450469</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1135774763851138</v>
+        <v>0.1135774763851155</v>
       </c>
       <c r="D2" t="n">
-        <v>1.693678881334918</v>
+        <v>1.693678881334915</v>
       </c>
       <c r="E2" t="n">
-        <v>2.138894407674461</v>
+        <v>2.138894407674464</v>
       </c>
       <c r="F2" t="n">
-        <v>7.222578944537179e-64</v>
+        <v>7.222578944566633e-64</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1492,16 +1492,16 @@
         <v>-0.01050744562892867</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02313482841481902</v>
+        <v>0.02313482841481903</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05585087611048782</v>
+        <v>-0.05585087611048783</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03483598485263048</v>
+        <v>0.03483598485263049</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6496971222641865</v>
+        <v>0.6496971222641869</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1517,16 +1517,16 @@
         <v>-0.03640287469709131</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05763586703459975</v>
+        <v>0.05763586703459977</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1493670983026462</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07656134890846358</v>
+        <v>0.07656134890846361</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5276475939331997</v>
+        <v>0.5276475939331999</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01048610640451848</v>
+        <v>-0.01048610640451846</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03813868767857897</v>
+        <v>0.03813868767857902</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08523656067215478</v>
+        <v>-0.08523656067215485</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06426434786311781</v>
+        <v>0.06426434786311794</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7833571861041332</v>
+        <v>0.783357186104134</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001511275113782342</v>
+        <v>-0.001511275113782287</v>
       </c>
       <c r="C6" t="n">
         <v>0.04211864645461957</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08406230524241233</v>
+        <v>-0.08406230524241229</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08103975501484766</v>
+        <v>0.08103975501484773</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9713769437607239</v>
+        <v>0.9713769437607249</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.06364683252462017</v>
+        <v>-0.06364683252462019</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04016802682897486</v>
+        <v>0.04016802682897489</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1423747184394495</v>
+        <v>-0.1423747184394496</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01508105339020918</v>
+        <v>0.01508105339020922</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1130766190665092</v>
+        <v>0.1130766190665095</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06421840671360726</v>
+        <v>-0.06421840671360725</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04041046821576312</v>
+        <v>0.04041046821576316</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1434214690149035</v>
+        <v>-0.1434214690149036</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01498465558768904</v>
+        <v>0.01498465558768913</v>
       </c>
       <c r="F8" t="n">
-        <v>0.112025910877008</v>
+        <v>0.1120259108770085</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1642,16 +1642,16 @@
         <v>-0.02659716766236244</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0389093015346309</v>
+        <v>0.03890930153463093</v>
       </c>
       <c r="D9" t="n">
         <v>-0.1028579973338481</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04966366200912317</v>
+        <v>0.04966366200912323</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4942477661537685</v>
+        <v>0.4942477661537688</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.08243544392281296</v>
+        <v>-0.08243544392281284</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06337665689811478</v>
+        <v>0.06337665689811482</v>
       </c>
       <c r="D10" t="n">
         <v>-0.2066514089036699</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04178052105804399</v>
+        <v>0.0417805210580442</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1933534561005047</v>
+        <v>0.1933534561005057</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1692,16 +1692,16 @@
         <v>-0.1356569674250366</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06253796406675879</v>
+        <v>0.06253796406675885</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2582291246623439</v>
+        <v>-0.258229124662344</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01308481018772932</v>
+        <v>-0.01308481018772924</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03006796939972206</v>
+        <v>0.03006796939972217</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1007904685653378</v>
+        <v>-0.1007904685653379</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06371050484176433</v>
+        <v>0.06371050484176442</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2256607634920607</v>
+        <v>-0.2256607634920609</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02407982636138498</v>
+        <v>0.02407982636138514</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1136479584008973</v>
+        <v>0.1136479584008977</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.006633880711504852</v>
+        <v>-0.006633880711504859</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06033231536084661</v>
+        <v>0.06033231536084677</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1248830459226769</v>
+        <v>-0.1248830459226772</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1116152844996672</v>
+        <v>0.1116152844996675</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9124445246059457</v>
+        <v>0.9124445246059459</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04852525054058577</v>
+        <v>-0.04852525054058585</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06115009346785072</v>
+        <v>0.0611500934678508</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1683772313888312</v>
+        <v>-0.1683772313888315</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07132673030765965</v>
+        <v>0.07132673030765974</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4274613181377219</v>
+        <v>0.4274613181377217</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1792,16 +1792,16 @@
         <v>-0.1427721540964336</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06497885750391966</v>
+        <v>0.06497885750391977</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2701283745606764</v>
+        <v>-0.2701283745606766</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01541593363219082</v>
+        <v>-0.01541593363219063</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02800549722683524</v>
+        <v>0.02800549722683549</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.09890443698017599</v>
+        <v>-0.09890443698017604</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05966171038444365</v>
+        <v>0.05966171038444369</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2158392405897449</v>
+        <v>-0.215839240589745</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0180303666293929</v>
+        <v>0.01803036662939295</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09736713642719751</v>
+        <v>0.09736713642719758</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.08736850131641771</v>
+        <v>-0.08736850131641773</v>
       </c>
       <c r="C17" t="n">
-        <v>0.06144897675671648</v>
+        <v>0.06144897675671651</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2078062826464209</v>
+        <v>-0.207806282646421</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03306928001358549</v>
+        <v>0.03306928001358553</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1550826837763965</v>
+        <v>0.1550826837763966</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06583221967935284</v>
+        <v>-0.06583221967935282</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0614250927970466</v>
+        <v>0.06142509279704649</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1862231893085949</v>
+        <v>-0.1862231893085946</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0545587499498892</v>
+        <v>0.05455874994988899</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2838332398704616</v>
+        <v>0.2838332398704608</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03558523015264693</v>
+        <v>-0.03558523015264695</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06209835410094822</v>
+        <v>0.06209835410094817</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1572957676897206</v>
+        <v>-0.1572957676897205</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08612530738442674</v>
+        <v>0.08612530738442661</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5666133660035837</v>
+        <v>0.5666133660035833</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.08036967353394858</v>
+        <v>-0.08036967353394864</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06209993601337647</v>
+        <v>0.06209993601337659</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2020833115624083</v>
+        <v>-0.2020833115624086</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04134396449451118</v>
+        <v>0.04134396449451135</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1955967007635249</v>
+        <v>0.1955967007635255</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1942,16 +1942,16 @@
         <v>-0.08492429139988221</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06272335023210063</v>
+        <v>0.06272335023210077</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2078597988444915</v>
+        <v>-0.2078597988444917</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03801121604472706</v>
+        <v>0.03801121604472733</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1757522723372701</v>
+        <v>0.175752272337271</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.04976148596577821</v>
+        <v>-0.04976148596577828</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06616872223007156</v>
+        <v>0.06616872223007154</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1794497984397533</v>
+        <v>-0.1794497984397534</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07992682650819691</v>
+        <v>0.0799268265081968</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4520273669320792</v>
+        <v>0.4520273669320783</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07216349561442491</v>
+        <v>-0.07216349561442494</v>
       </c>
       <c r="C23" t="n">
         <v>0.06023148981336574</v>
@@ -1998,10 +1998,10 @@
         <v>-0.1902150463838129</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04588805515496308</v>
+        <v>0.04588805515496305</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2308771345223999</v>
+        <v>0.2308771345223998</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.002140600051701927</v>
+        <v>-0.002140600051701965</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05102175602657195</v>
+        <v>0.05102175602657193</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1021414042917724</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09786020418836855</v>
+        <v>0.09786020418836847</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9665348482046917</v>
+        <v>0.9665348482046912</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03377723702718432</v>
+        <v>0.03377723702718428</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02826966249252098</v>
+        <v>0.02826966249252097</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02163028331325962</v>
+        <v>-0.02163028331325964</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08918475736762826</v>
+        <v>0.0891847573676282</v>
       </c>
       <c r="F25" t="n">
-        <v>0.232156273970697</v>
+        <v>0.2321562739706974</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01185029725512765</v>
+        <v>0.0118502972551276</v>
       </c>
       <c r="C26" t="n">
         <v>0.03531972237812556</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05737508654995183</v>
+        <v>-0.05737508654995188</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08107568106020713</v>
+        <v>0.08107568106020707</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7372366186039934</v>
+        <v>0.7372366186039944</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04710001854922439</v>
+        <v>0.04710001854922437</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03670272747213621</v>
+        <v>0.03670272747213622</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0248360054305514</v>
+        <v>-0.02483600543055144</v>
       </c>
       <c r="E27" t="n">
         <v>0.1190360425290002</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1993926378384789</v>
+        <v>0.1993926378384792</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02791509950305223</v>
+        <v>0.0279150995030522</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03688860617765243</v>
+        <v>0.03688860617765245</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.04438524004502829</v>
+        <v>-0.04438524004502835</v>
       </c>
       <c r="E28" t="n">
         <v>0.1002154390511327</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4492053910316429</v>
+        <v>0.4492053910316437</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002028448287522435</v>
+        <v>0.002028448287522409</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03699514228435766</v>
+        <v>0.03699514228435767</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07048069819275345</v>
+        <v>-0.07048069819275349</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07453759476779832</v>
+        <v>0.07453759476779831</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9562737999639482</v>
+        <v>0.9562737999639488</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.008532607932754597</v>
+        <v>-0.008532607932754718</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0474334909408585</v>
+        <v>0.04743349094085851</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1015005418378442</v>
+        <v>-0.1015005418378443</v>
       </c>
       <c r="E30" t="n">
-        <v>0.08443532597233498</v>
+        <v>0.08443532597233488</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8572422817678189</v>
+        <v>0.8572422817678169</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.002599540092059323</v>
+        <v>0.4341439838076169</v>
       </c>
       <c r="C31" t="n">
-        <v>0.005215369690511485</v>
+        <v>0.01233167034636807</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.007622396667404996</v>
+        <v>0.4099743540595149</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01282147685152364</v>
+        <v>0.4583136135557189</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6181751351723377</v>
+        <v>1.640909443405939e-271</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4341439838076169</v>
+        <v>-0.0004392159488227707</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01233167034636804</v>
+        <v>0.001854819509338051</v>
       </c>
       <c r="D32" t="n">
-        <v>0.409974354059515</v>
+        <v>-0.004074595384947605</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4583136135557189</v>
+        <v>0.003196163487302064</v>
       </c>
       <c r="F32" t="n">
-        <v>1.640909443400152e-271</v>
+        <v>0.8128141730106098</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0004392159488227687</v>
+        <v>0.0001837898545406304</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001854819509338078</v>
+        <v>0.001724872936764035</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004074595384947656</v>
+        <v>-0.003196898979424713</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003196163487302118</v>
+        <v>0.003564478688505974</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8128141730106133</v>
+        <v>0.9151438512506996</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0009410812065911193</v>
+        <v>0.0009410812065911147</v>
       </c>
       <c r="C34" t="n">
         <v>0.001598281733026356</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.002191493427288801</v>
+        <v>-0.002191493427288804</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00407365584047104</v>
+        <v>0.004073655840471034</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5559900216047673</v>
+        <v>0.555990021604769</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0001837898545406331</v>
+        <v>0.002599540092059322</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001724872936764036</v>
+        <v>0.005215369690511499</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.003196898979424712</v>
+        <v>-0.007622396667405024</v>
       </c>
       <c r="E35" t="n">
-        <v>0.003564478688505978</v>
+        <v>0.01282147685152367</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9151438512506984</v>
+        <v>0.6181751351723388</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.338987226254025</v>
+        <v>-2.338987226254024</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5055991410637978</v>
+        <v>0.5055991410637918</v>
       </c>
       <c r="D2" t="n">
-        <v>3.724908496213204e-06</v>
+        <v>3.724908496212245e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01256293251776085</v>
+        <v>0.01256293251776077</v>
       </c>
       <c r="C3" t="n">
         <v>0.1067715806898984</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9063356642598708</v>
+        <v>0.9063356642598713</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3234998731582308</v>
+        <v>0.3234998731582306</v>
       </c>
       <c r="C4" t="n">
         <v>0.2296824580519299</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1589932049199887</v>
+        <v>0.1589932049199888</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7738634278997921</v>
+        <v>0.773863427899792</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1687469244012597</v>
+        <v>0.1687469244012598</v>
       </c>
       <c r="D5" t="n">
-        <v>4.519463710118297e-06</v>
+        <v>4.519463710118381e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1783768596808243</v>
+        <v>-0.1783768596808241</v>
       </c>
       <c r="C6" t="n">
         <v>0.2079311667841183</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3909670410803541</v>
+        <v>0.3909670410803544</v>
       </c>
     </row>
     <row r="7">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1377408491060987</v>
+        <v>0.1377408491060986</v>
       </c>
       <c r="C7" t="n">
         <v>0.1831232046369752</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4519453245419603</v>
+        <v>0.4519453245419608</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09506786697132874</v>
+        <v>-0.09506786697132887</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1943228459617253</v>
+        <v>0.1943228459617255</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6246814188469618</v>
+        <v>0.6246814188469617</v>
       </c>
     </row>
     <row r="9">
@@ -2468,7 +2468,7 @@
         <v>0.1651060633318497</v>
       </c>
       <c r="D9" t="n">
-        <v>8.571962941862631e-11</v>
+        <v>8.571962941862759e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1122239612642833</v>
+        <v>0.1122239612642835</v>
       </c>
       <c r="C10" t="n">
         <v>0.2836642639672833</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6923835464094221</v>
+        <v>0.6923835464094216</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2622355198708376</v>
+        <v>0.2622355198708377</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2783540080934938</v>
+        <v>0.2783540080934941</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3461447386877406</v>
+        <v>0.3461447386877412</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1888101216478686</v>
+        <v>-0.1888101216478687</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3063764302491637</v>
+        <v>0.306376430249163</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5377173713587788</v>
+        <v>0.5377173713587777</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3127315418553179</v>
+        <v>0.3127315418553178</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2741146153277014</v>
+        <v>0.2741146153277019</v>
       </c>
       <c r="D13" t="n">
-        <v>0.253920380260887</v>
+        <v>0.253920380260888</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2705944435743411</v>
+        <v>0.2705944435743409</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2618702913171512</v>
+        <v>0.2618702913171503</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3014566107781707</v>
+        <v>0.3014566107781694</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3028665560997512</v>
+        <v>0.3028665560997513</v>
       </c>
       <c r="C15" t="n">
         <v>0.2681769459926689</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2587487663172148</v>
+        <v>0.2587487663172143</v>
       </c>
     </row>
     <row r="16">
@@ -2577,10 +2577,10 @@
         <v>0.1363845397670079</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2557002711895606</v>
+        <v>0.2557002711895608</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5937729164140201</v>
+        <v>0.5937729164140206</v>
       </c>
     </row>
     <row r="17">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1940322365781457</v>
+        <v>0.1940322365781456</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2735957160328508</v>
+        <v>0.2735957160328507</v>
       </c>
       <c r="D17" t="n">
         <v>0.4782045582119668</v>
@@ -2609,10 +2609,10 @@
         <v>0.4857181530086623</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2539438750025471</v>
+        <v>0.2539438750025463</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0557866188660513</v>
+        <v>0.05578661886605048</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1221030286982098</v>
+        <v>0.1221030286982097</v>
       </c>
       <c r="C19" t="n">
         <v>0.2803928791452491</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6632204259123764</v>
+        <v>0.6632204259123766</v>
       </c>
     </row>
     <row r="20">
@@ -2641,10 +2641,10 @@
         <v>0.257910666551023</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2808417151108229</v>
+        <v>0.2808417151108216</v>
       </c>
       <c r="D20" t="n">
-        <v>0.358436259444231</v>
+        <v>0.3584362594442287</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2543410650746324</v>
+        <v>0.2543410650746321</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2766729067347433</v>
+        <v>0.2766729067347432</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3579468768346249</v>
+        <v>0.3579468768346254</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.006839691327090229</v>
+        <v>0.006839691327090175</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2924114759179867</v>
+        <v>0.2924114759179862</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9813386718121052</v>
+        <v>0.9813386718121053</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07476694074869081</v>
+        <v>-0.07476694074869106</v>
       </c>
       <c r="C23" t="n">
-        <v>0.292367449380384</v>
+        <v>0.2923674493803828</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7981598227109671</v>
+        <v>0.7981598227109656</v>
       </c>
     </row>
     <row r="24">
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.892238582155323</v>
+        <v>0.8922385821553231</v>
       </c>
       <c r="C24" t="n">
         <v>0.1585806900026265</v>
@@ -2721,10 +2721,10 @@
         <v>-0.5774441439879955</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1158769831635338</v>
+        <v>0.1158769831635337</v>
       </c>
       <c r="D25" t="n">
-        <v>6.252461417905484e-07</v>
+        <v>6.252461417905463e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.148537219965026</v>
+        <v>-0.1485372199650261</v>
       </c>
       <c r="C26" t="n">
         <v>0.1534302542675076</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3329899032073059</v>
+        <v>0.3329899032073057</v>
       </c>
     </row>
     <row r="27">
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08883446031032111</v>
+        <v>-0.08883446031032109</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1507497724290651</v>
+        <v>0.150749772429065</v>
       </c>
       <c r="D27" t="n">
         <v>0.5556706364059293</v>
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05597729137794841</v>
+        <v>-0.05597729137794842</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1541767646161668</v>
+        <v>0.1541767646161666</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7165509786784033</v>
+        <v>0.716550978678403</v>
       </c>
     </row>
     <row r="29">
@@ -2785,58 +2785,58 @@
         <v>-0.3669690670720732</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1613874819745224</v>
+        <v>0.1613874819745223</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02297569956216942</v>
+        <v>0.0229756995621693</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0174647800117059</v>
+        <v>0.02286123471747222</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0227940904205145</v>
+        <v>0.05080677610550082</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4435586673664915</v>
+        <v>0.6527361927410917</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.02286123471747219</v>
+        <v>-0.01284483543314758</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05080677610550104</v>
+        <v>0.008409368149555639</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6527361927410935</v>
+        <v>0.1266507454755514</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.01284483543314755</v>
+        <v>0.01392592672011598</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008409368149555754</v>
+        <v>0.006893603746700861</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1266507454755573</v>
+        <v>0.04337064213536521</v>
       </c>
     </row>
     <row r="33">
@@ -2846,10 +2846,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.007242589222325578</v>
+        <v>0.007242589222325576</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006273236664278017</v>
+        <v>0.006273236664278018</v>
       </c>
       <c r="D33" t="n">
         <v>0.248286258165366</v>
@@ -2858,17 +2858,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01392592672011598</v>
+        <v>-0.01746478001170588</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00689360374670087</v>
+        <v>0.02279409042051461</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04337064213536546</v>
+        <v>0.4435586673664942</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.095</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.015</v>
+        <v>-0.029</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08</v>
+        <v>0.042</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02</v>
+        <v>-0.095</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="E7" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.024</v>
+        <v>0.369</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02</v>
+        <v>0.36</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.216</v>
+        <v>-0.183</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.059</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.157</v>
+        <v>0.174</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.008</v>
+        <v>0.02</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.018</v>
+        <v>0.003</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.009999999999999998</v>
+        <v>0.017</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.082</v>
+        <v>0.015</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.028</v>
+        <v>0.017</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05400000000000001</v>
+        <v>-0.002000000000000002</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.117</v>
+        <v>0.008</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E13" t="n">
-        <v>0.113</v>
+        <v>0.002</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.015</v>
+        <v>-0.216</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002</v>
+        <v>-0.059</v>
       </c>
       <c r="E14" t="n">
-        <v>0.013</v>
+        <v>0.157</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.015</v>
+        <v>0.35</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.026</v>
+        <v>0.018</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.011</v>
+        <v>0.332</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.031</v>
+        <v>-0.082</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.005</v>
+        <v>-0.028</v>
       </c>
       <c r="E16" t="n">
-        <v>0.026</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.035</v>
+        <v>-0.117</v>
       </c>
       <c r="D17" t="n">
-        <v>0.022</v>
+        <v>-0.004</v>
       </c>
       <c r="E17" t="n">
-        <v>0.013</v>
+        <v>0.113</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.002</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.099</v>
+        <v>0.19</v>
       </c>
       <c r="D19" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.025</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.35</v>
+        <v>0.024</v>
       </c>
       <c r="D20" t="n">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="E20" t="n">
-        <v>0.332</v>
+        <v>0.02</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.036</v>
+        <v>0.099</v>
       </c>
       <c r="D21" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.028</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.045</v>
+        <v>-0.008</v>
       </c>
       <c r="D22" t="n">
-        <v>0.007</v>
+        <v>-0.018</v>
       </c>
       <c r="E22" t="n">
-        <v>0.038</v>
+        <v>-0.009999999999999998</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.183</v>
+        <v>-0.018</v>
       </c>
       <c r="D24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="E24" t="n">
-        <v>0.174</v>
+        <v>0.013</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.029</v>
+        <v>-0.005</v>
       </c>
       <c r="E25" t="n">
-        <v>0.042</v>
+        <v>0.026</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.369</v>
+        <v>0.003</v>
       </c>
       <c r="D26" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.36</v>
+        <v>0.002</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.011</v>
+        <v>0.035</v>
       </c>
       <c r="D27" t="n">
-        <v>0.003</v>
+        <v>0.022</v>
       </c>
       <c r="E27" t="n">
-        <v>0.008</v>
+        <v>0.013</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.003</v>
+        <v>-0.015</v>
       </c>
       <c r="D28" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="E28" t="n">
-        <v>0.002</v>
+        <v>0.013</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.015</v>
+        <v>0.036</v>
       </c>
       <c r="D29" t="n">
-        <v>0.017</v>
+        <v>0.008</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.002000000000000002</v>
+        <v>0.028</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.018</v>
+        <v>0.045</v>
       </c>
       <c r="D30" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="E30" t="n">
-        <v>0.013</v>
+        <v>0.038</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.19</v>
+        <v>-0.015</v>
       </c>
       <c r="D31" t="n">
-        <v>0.025</v>
+        <v>-0.026</v>
       </c>
       <c r="E31" t="n">
-        <v>0.165</v>
+        <v>-0.011</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1467,16 +1467,16 @@
         <v>1.91628664450469</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1135774763851165</v>
+        <v>0.1135774763851155</v>
       </c>
       <c r="D2" t="n">
-        <v>1.693678881334913</v>
+        <v>1.693678881334915</v>
       </c>
       <c r="E2" t="n">
-        <v>2.138894407674467</v>
+        <v>2.138894407674464</v>
       </c>
       <c r="F2" t="n">
-        <v>7.222578944584555e-64</v>
+        <v>7.222578944567049e-64</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.01050744562892866</v>
+        <v>-0.01050744562892867</v>
       </c>
       <c r="C3" t="n">
         <v>0.02313482841481903</v>
@@ -1498,10 +1498,10 @@
         <v>-0.05585087611048783</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03483598485263051</v>
+        <v>0.03483598485263049</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6496971222641871</v>
+        <v>0.6496971222641867</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03640287469709135</v>
+        <v>-0.03640287469709134</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05763586703459977</v>
+        <v>0.05763586703459976</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1493670983026463</v>
+        <v>-0.1493670983026462</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07656134890846358</v>
+        <v>0.07656134890846356</v>
       </c>
       <c r="F4" t="n">
         <v>0.5276475939331995</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01048610640451849</v>
+        <v>-0.01048610640451848</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03813868767857899</v>
+        <v>0.03813868767857898</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08523656067215482</v>
+        <v>-0.08523656067215479</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06426434786311785</v>
+        <v>0.06426434786311783</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7833571861041332</v>
+        <v>0.7833571861041333</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001511275113782194</v>
+        <v>-0.001511275113782305</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04211864645461955</v>
+        <v>0.04211864645461956</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08406230524241216</v>
+        <v>-0.08406230524241229</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08103975501484777</v>
+        <v>0.08103975501484767</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9713769437607267</v>
+        <v>0.9713769437607246</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06421840671360726</v>
+        <v>-0.06421840671360723</v>
       </c>
       <c r="C8" t="n">
         <v>0.04041046821576315</v>
@@ -1623,10 +1623,10 @@
         <v>-0.1434214690149036</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01498465558768909</v>
+        <v>0.01498465558768912</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1120259108770083</v>
+        <v>0.1120259108770084</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02659716766236246</v>
+        <v>-0.02659716766236244</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03890930153463094</v>
+        <v>0.03890930153463092</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1028579973338482</v>
+        <v>-0.1028579973338481</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04966366200912323</v>
+        <v>0.04966366200912322</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4942477661537685</v>
+        <v>0.4942477661537688</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.08243544392281291</v>
+        <v>-0.08243544392281278</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06337665689811477</v>
+        <v>0.06337665689811495</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2066514089036698</v>
+        <v>-0.2066514089036701</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04178052105804402</v>
+        <v>0.04178052105804449</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1933534561005049</v>
+        <v>0.193353456100507</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1356569674250367</v>
+        <v>-0.1356569674250366</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06253796406675889</v>
+        <v>0.06253796406675893</v>
       </c>
       <c r="D11" t="n">
         <v>-0.2582291246623442</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01308481018772921</v>
+        <v>-0.01308481018772904</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03006796939972221</v>
+        <v>0.03006796939972241</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1007904685653379</v>
+        <v>-0.1007904685653378</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06371050484176442</v>
+        <v>0.06371050484176438</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2256607634920609</v>
+        <v>-0.2256607634920607</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02407982636138509</v>
+        <v>0.02407982636138513</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1136479584008975</v>
+        <v>0.1136479584008977</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.006633880711504913</v>
+        <v>-0.006633880711504789</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06033231536084671</v>
+        <v>0.06033231536084689</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1248830459226771</v>
+        <v>-0.1248830459226774</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1116152844996673</v>
+        <v>0.1116152844996678</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9124445246059452</v>
+        <v>0.912444524605947</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04852525054058594</v>
+        <v>-0.04852525054058562</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06115009346785085</v>
+        <v>0.06115009346785094</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1683772313888316</v>
+        <v>-0.1683772313888315</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07132673030765974</v>
+        <v>0.07132673030766024</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4274613181377213</v>
+        <v>0.427461318137725</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1427721540964337</v>
+        <v>-0.1427721540964335</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06497885750391974</v>
+        <v>0.06497885750391988</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2701283745606766</v>
+        <v>-0.2701283745606767</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01541593363219074</v>
+        <v>-0.01541593363219035</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02800549722683537</v>
+        <v>0.02800549722683584</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.09890443698017612</v>
+        <v>-0.09890443698017594</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0596617103844438</v>
+        <v>0.05966171038444381</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2158392405897453</v>
+        <v>-0.2158392405897451</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01803036662939306</v>
+        <v>0.01803036662939327</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09736713642719785</v>
+        <v>0.09736713642719856</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.0873685013164178</v>
+        <v>-0.0873685013164177</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0614489767567166</v>
+        <v>0.06144897675671667</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2078062826464212</v>
+        <v>-0.2078062826464213</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03306928001358564</v>
+        <v>0.03306928001358587</v>
       </c>
       <c r="F17" t="n">
-        <v>0.155082683776397</v>
+        <v>0.1550826837763979</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06583221967935289</v>
+        <v>-0.06583221967935286</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06142509279704668</v>
+        <v>0.06142509279704669</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1862231893085951</v>
+        <v>-0.186223189308595</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0545587499498893</v>
+        <v>0.05455874994988934</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2838332398704617</v>
+        <v>0.2838332398704622</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03558523015264702</v>
+        <v>-0.03558523015264693</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06209835410094822</v>
+        <v>0.06209835410094836</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1572957676897207</v>
+        <v>-0.1572957676897209</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08612530738442667</v>
+        <v>0.08612530738442702</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5666133660035829</v>
+        <v>0.5666133660035846</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.08036967353394864</v>
+        <v>-0.08036967353394857</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06209993601337668</v>
+        <v>0.06209993601337672</v>
       </c>
       <c r="D20" t="n">
         <v>-0.2020833115624088</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04134396449451153</v>
+        <v>0.04134396449451166</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1955967007635262</v>
+        <v>0.1955967007635266</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.08492429139988233</v>
+        <v>-0.08492429139988215</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06272335023210079</v>
+        <v>0.06272335023210092</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2078597988444919</v>
+        <v>-0.207859798844492</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03801121604472726</v>
+        <v>0.03801121604472768</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1757522723372706</v>
+        <v>0.1757522723372724</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.04976148596577851</v>
+        <v>-0.04976148596577843</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06616872223007157</v>
+        <v>0.0661687222300717</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1794497984397536</v>
+        <v>-0.1794497984397538</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07992682650819663</v>
+        <v>0.07992682650819696</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4520273669320766</v>
+        <v>0.4520273669320781</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07216349561442496</v>
+        <v>-0.07216349561442485</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06023148981336576</v>
+        <v>0.06023148981336584</v>
       </c>
       <c r="D23" t="n">
         <v>-0.190215046383813</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04588805515496307</v>
+        <v>0.04588805515496333</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2308771345223998</v>
+        <v>0.230877134522401</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.002140600051701934</v>
+        <v>-0.002140600051701927</v>
       </c>
       <c r="C24" t="n">
         <v>0.05102175602657195</v>
@@ -2026,7 +2026,7 @@
         <v>0.09786020418836855</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9665348482046916</v>
+        <v>0.9665348482046917</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03377723702718437</v>
+        <v>0.03377723702718431</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02826966249252101</v>
+        <v>0.02826966249252098</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02163028331325963</v>
+        <v>-0.02163028331325964</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08918475736762838</v>
+        <v>0.08918475736762825</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2321562739706969</v>
+        <v>0.2321562739706973</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01185029725512754</v>
+        <v>0.01185029725512757</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03531972237812557</v>
+        <v>0.03531972237812558</v>
       </c>
       <c r="D26" t="n">
         <v>-0.05737508654995196</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08107568106020704</v>
+        <v>0.0810756810602071</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7372366186039958</v>
+        <v>0.7372366186039951</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04710001854922437</v>
+        <v>0.04710001854922434</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03670272747213627</v>
+        <v>0.03670272747213622</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.02483600543055153</v>
+        <v>-0.02483600543055148</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1190360425290003</v>
+        <v>0.1190360425290002</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1993926378384797</v>
+        <v>0.1993926378384795</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2117,16 +2117,16 @@
         <v>0.02791509950305224</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03688860617765249</v>
+        <v>0.03688860617765245</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.04438524004502839</v>
+        <v>-0.04438524004502832</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1002154390511329</v>
+        <v>0.1002154390511328</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4492053910316435</v>
+        <v>0.4492053910316429</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002028448287522394</v>
+        <v>0.002028448287522432</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03699514228435769</v>
+        <v>0.03699514228435765</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07048069819275354</v>
+        <v>-0.07048069819275343</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07453759476779834</v>
+        <v>0.07453759476779828</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9562737999639492</v>
+        <v>0.9562737999639483</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.008532607932754689</v>
+        <v>-0.008532607932754567</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0474334909408585</v>
+        <v>0.04743349094085852</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1015005418378443</v>
+        <v>-0.1015005418378442</v>
       </c>
       <c r="E30" t="n">
-        <v>0.08443532597233488</v>
+        <v>0.08443532597233505</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8572422817678174</v>
+        <v>0.8572422817678194</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4341439838076168</v>
+        <v>0.0009410812065911163</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01233167034636806</v>
+        <v>0.001598281733026354</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4099743540595149</v>
+        <v>-0.0021914934272888</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4583136135557188</v>
+        <v>0.004073655840471033</v>
       </c>
       <c r="F31" t="n">
-        <v>1.640909443404259e-271</v>
+        <v>0.5559900216047681</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0001837898545406308</v>
+        <v>0.002599540092059309</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001724872936764038</v>
+        <v>0.005215369690511525</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.003196898979424717</v>
+        <v>-0.007622396667405088</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003564478688505979</v>
+        <v>0.01282147685152371</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9151438512506995</v>
+        <v>0.6181751351723421</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002599540092059321</v>
+        <v>0.4341439838076169</v>
       </c>
       <c r="C33" t="n">
-        <v>0.005215369690511481</v>
+        <v>0.01233167034636802</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.007622396667404991</v>
+        <v>0.409974354059515</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01282147685152363</v>
+        <v>0.4583136135557188</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6181751351723377</v>
+        <v>1.640909443398472e-271</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.0004392159488227686</v>
+        <v>-0.0004392159488227713</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001854819509338072</v>
+        <v>0.001854819509338099</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004074595384947644</v>
+        <v>-0.004074595384947699</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003196163487302108</v>
+        <v>0.003196163487302156</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8128141730106128</v>
+        <v>0.8128141730106142</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0009410812065911139</v>
+        <v>0.0001837898545406305</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001598281733026353</v>
+        <v>0.001724872936764038</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0021914934272888</v>
+        <v>-0.003196898979424717</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004073655840471029</v>
+        <v>0.003564478688505979</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5559900216047687</v>
+        <v>0.9151438512506996</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.338987226254024</v>
+        <v>-2.338987226254026</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5055991410638138</v>
+        <v>0.5055991410638002</v>
       </c>
       <c r="D2" t="n">
-        <v>3.724908496215856e-06</v>
+        <v>3.724908496213564e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01256293251776086</v>
+        <v>0.01256293251776077</v>
       </c>
       <c r="C3" t="n">
         <v>0.1067715806898984</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9063356642598707</v>
+        <v>0.9063356642598713</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3234998731582306</v>
+        <v>0.3234998731582304</v>
       </c>
       <c r="C4" t="n">
         <v>0.2296824580519299</v>
       </c>
       <c r="D4" t="n">
-        <v>0.158993204919989</v>
+        <v>0.1589932049199891</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7738634278997921</v>
+        <v>0.773863427899792</v>
       </c>
       <c r="C5" t="n">
-        <v>0.16874692440126</v>
+        <v>0.1687469244012597</v>
       </c>
       <c r="D5" t="n">
-        <v>4.519463710118472e-06</v>
+        <v>4.519463710118322e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1783768596808243</v>
+        <v>-0.1783768596808241</v>
       </c>
       <c r="C6" t="n">
         <v>0.2079311667841184</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3909670410803542</v>
+        <v>0.3909670410803546</v>
       </c>
     </row>
     <row r="7">
@@ -2433,10 +2433,10 @@
         <v>0.1377408491060986</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1831232046369754</v>
+        <v>0.1831232046369752</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4519453245419613</v>
+        <v>0.4519453245419608</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09506786697132875</v>
+        <v>-0.09506786697132878</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1943228459617256</v>
+        <v>0.1943228459617254</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6246814188469623</v>
+        <v>0.6246814188469619</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.071572205240918</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1651060633318498</v>
+        <v>0.1651060633318495</v>
       </c>
       <c r="D9" t="n">
-        <v>8.57196294186304e-11</v>
+        <v>8.571962941862318e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2481,10 +2481,10 @@
         <v>0.1122239612642838</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2836642639672838</v>
+        <v>0.2836642639672835</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6923835464094215</v>
+        <v>0.692383546409421</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2622355198708382</v>
+        <v>0.2622355198708383</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2783540080934942</v>
+        <v>0.278354008093494</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3461447386877404</v>
+        <v>0.3461447386877399</v>
       </c>
     </row>
     <row r="12">
@@ -2513,10 +2513,10 @@
         <v>-0.1888101216478681</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3063764302491628</v>
+        <v>0.306376430249163</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5377173713587788</v>
+        <v>0.5377173713587791</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3127315418553182</v>
+        <v>0.3127315418553183</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2741146153277016</v>
+        <v>0.2741146153277019</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2539203802608869</v>
+        <v>0.2539203802608874</v>
       </c>
     </row>
     <row r="14">
@@ -2545,10 +2545,10 @@
         <v>0.2705944435743414</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2618702913171513</v>
+        <v>0.2618702913171503</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3014566107781703</v>
+        <v>0.3014566107781685</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3028665560997518</v>
+        <v>0.3028665560997519</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2681769459926692</v>
+        <v>0.2681769459926687</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2587487663172143</v>
+        <v>0.2587487663172132</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1363845397670083</v>
+        <v>0.1363845397670084</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2557002711895612</v>
+        <v>0.2557002711895613</v>
       </c>
       <c r="D16" t="n">
-        <v>0.59377291641402</v>
+        <v>0.5937729164140199</v>
       </c>
     </row>
     <row r="17">
@@ -2593,10 +2593,10 @@
         <v>0.1940322365781461</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2735957160328507</v>
+        <v>0.2735957160328512</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4782045582119657</v>
+        <v>0.4782045582119665</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>0.4857181530086626</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2539438750025466</v>
+        <v>0.2539438750025474</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05578661886605062</v>
+        <v>0.05578661886605148</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1221030286982103</v>
+        <v>0.1221030286982102</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2803928791452494</v>
+        <v>0.2803928791452489</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6632204259123754</v>
+        <v>0.6632204259123748</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2579106665510233</v>
+        <v>0.2579106665510235</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2808417151108225</v>
+        <v>0.2808417151108231</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3584362594442296</v>
+        <v>0.3584362594442305</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2543410650746327</v>
+        <v>0.2543410650746326</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2766729067347437</v>
+        <v>0.2766729067347436</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3579468768346251</v>
+        <v>0.3579468768346252</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.006839691327090471</v>
+        <v>0.006839691327090622</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2924114759179866</v>
+        <v>0.2924114759179859</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9813386718121045</v>
+        <v>0.9813386718121041</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07476694074869057</v>
+        <v>-0.07476694074869027</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2923674493803833</v>
+        <v>0.2923674493803832</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7981598227109672</v>
+        <v>0.798159822710968</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8922385821553229</v>
+        <v>0.8922385821553231</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1585806900026266</v>
+        <v>0.1585806900026265</v>
       </c>
       <c r="D24" t="n">
-        <v>1.840081150019105e-08</v>
+        <v>1.840081150019075e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5774441439879956</v>
+        <v>-0.5774441439879955</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1158769831635337</v>
+        <v>0.1158769831635338</v>
       </c>
       <c r="D25" t="n">
-        <v>6.252461417905323e-07</v>
+        <v>6.252461417905612e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.148537219965026</v>
+        <v>-0.1485372199650264</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1534302542675076</v>
+        <v>0.1534302542675077</v>
       </c>
       <c r="D26" t="n">
-        <v>0.332989903207306</v>
+        <v>0.3329899032073051</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08883446031032097</v>
+        <v>-0.08883446031032111</v>
       </c>
       <c r="C27" t="n">
         <v>0.150749772429065</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5556706364059296</v>
+        <v>0.5556706364059292</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05597729137794832</v>
+        <v>-0.0559772913779484</v>
       </c>
       <c r="C28" t="n">
         <v>0.1541767646161667</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7165509786784037</v>
+        <v>0.7165509786784032</v>
       </c>
     </row>
     <row r="29">
@@ -2782,61 +2782,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.366969067072073</v>
+        <v>-0.3669690670720732</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1613874819745224</v>
+        <v>0.1613874819745222</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02297569956216942</v>
+        <v>0.02297569956216924</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.02286123471747216</v>
+        <v>0.00724258922232558</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05080677610550113</v>
+        <v>0.006273236664278034</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6527361927410945</v>
+        <v>0.2482862581653671</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01392592672011598</v>
+        <v>-0.01746478001170589</v>
       </c>
       <c r="C31" t="n">
-        <v>0.006893603746700875</v>
+        <v>0.02279409042051449</v>
       </c>
       <c r="D31" t="n">
-        <v>0.04337064213536566</v>
+        <v>0.4435586673664915</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.01746478001170591</v>
+        <v>0.02286123471747234</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02279409042051463</v>
+        <v>0.05080677610550093</v>
       </c>
       <c r="D32" t="n">
-        <v>0.443558667366494</v>
+        <v>0.6527361927410906</v>
       </c>
     </row>
     <row r="33">
@@ -2846,29 +2846,29 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.01284483543314758</v>
+        <v>-0.01284483543314756</v>
       </c>
       <c r="C33" t="n">
-        <v>0.008409368149555781</v>
+        <v>0.008409368149555702</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1266507454755577</v>
+        <v>0.1266507454755547</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.00724258922232557</v>
+        <v>0.01392592672011598</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006273236664278007</v>
+        <v>0.006893603746700875</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2482862581653656</v>
+        <v>0.04337064213536566</v>
       </c>
     </row>
   </sheetData>
